--- a/Exp3_PTO_GRPO/eda/results/lookahead/transfer/tables/transfer.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/lookahead/transfer/tables/transfer.xlsx
@@ -6324,40 +6324,40 @@
         <v>96</v>
       </c>
       <c r="F79" t="n">
-        <v>0.01642194320286509</v>
+        <v>0.03079348097967066</v>
       </c>
       <c r="G79" t="n">
-        <v>0.07141605396288182</v>
+        <v>0.1061087763685476</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.0285806954117087</v>
+        <v>-0.02489894940521917</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0610330111405868</v>
+        <v>0.08986541250738542</v>
       </c>
       <c r="J79" t="n">
-        <v>0.3209295212958708</v>
+        <v>0.2882616851318276</v>
       </c>
       <c r="K79" t="n">
-        <v>0.9573744584654621</v>
+        <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>0.01918483669795042</v>
+        <v>0.04583937353240927</v>
       </c>
       <c r="M79" t="n">
-        <v>0.08797454454846312</v>
+        <v>0.1686490186439506</v>
       </c>
       <c r="N79" t="n">
-        <v>-0.02401036427666259</v>
+        <v>-0.007031000803518131</v>
       </c>
       <c r="O79" t="n">
-        <v>0.06298190411534491</v>
+        <v>0.1002017154270401</v>
       </c>
       <c r="P79" t="n">
-        <v>0.4030558571143124</v>
+        <v>0.05998347556719329</v>
       </c>
       <c r="Q79" t="n">
-        <v>1</v>
+        <v>0.2399339022687731</v>
       </c>
       <c r="R79" t="b">
         <v>1</v>
@@ -6399,43 +6399,43 @@
         <v>96</v>
       </c>
       <c r="F80" t="n">
-        <v>0.003739852700008841</v>
+        <v>0.001017489159273047</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01787688324422572</v>
+        <v>0.003409939507699371</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.03754483819407545</v>
+        <v>-0.06070637510962799</v>
       </c>
       <c r="I80" t="n">
-        <v>0.04720027383513331</v>
+        <v>0.0595160801744581</v>
       </c>
       <c r="J80" t="n">
-        <v>0.735249483670841</v>
+        <v>0.9900317631590686</v>
       </c>
       <c r="K80" t="n">
-        <v>0.9573744584654621</v>
+        <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>0.01705049887477915</v>
+        <v>-0.002902446553928822</v>
       </c>
       <c r="M80" t="n">
-        <v>0.08161255945400382</v>
+        <v>-0.01151437128044597</v>
       </c>
       <c r="N80" t="n">
-        <v>-0.02297759175217473</v>
+        <v>-0.05295369439275305</v>
       </c>
       <c r="O80" t="n">
-        <v>0.05975375758303092</v>
+        <v>0.04688457028322041</v>
       </c>
       <c r="P80" t="n">
-        <v>0.79746771968048</v>
+        <v>0.7928442925781791</v>
       </c>
       <c r="Q80" t="n">
         <v>1</v>
       </c>
       <c r="R80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S80" t="b">
         <v>0</v>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>K0</t>
+          <t>K5</t>
         </is>
       </c>
     </row>
@@ -6474,37 +6474,37 @@
         <v>96</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.0116310844602737</v>
+        <v>-0.001592286235218503</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.04835535427360004</v>
+        <v>-0.005118838928302514</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.05777610074337322</v>
+        <v>-0.06253840355291937</v>
       </c>
       <c r="I81" t="n">
-        <v>0.03593588685016438</v>
+        <v>0.05919946862168794</v>
       </c>
       <c r="J81" t="n">
-        <v>0.3191248194884874</v>
+        <v>0.7270087285861426</v>
       </c>
       <c r="K81" t="n">
-        <v>0.9573744584654621</v>
+        <v>1</v>
       </c>
       <c r="L81" t="n">
-        <v>-0.00774697223300249</v>
+        <v>-0.01207601760783338</v>
       </c>
       <c r="M81" t="n">
-        <v>-0.03443679587148055</v>
+        <v>-0.04287473183881976</v>
       </c>
       <c r="N81" t="n">
-        <v>-0.04943901142809928</v>
+        <v>-0.06605307915836728</v>
       </c>
       <c r="O81" t="n">
-        <v>0.03551284569920097</v>
+        <v>0.04407874575868191</v>
       </c>
       <c r="P81" t="n">
-        <v>0.4655113624543473</v>
+        <v>0.4979085254150786</v>
       </c>
       <c r="Q81" t="n">
         <v>1</v>
@@ -6549,40 +6549,40 @@
         <v>96</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.03587967001437439</v>
+        <v>-0.007234099111454746</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.2007112821040763</v>
+        <v>-0.03066280375290178</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.07271036632225943</v>
+        <v>-0.05390041026061815</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.001072663138017283</v>
+        <v>0.03988775176274383</v>
       </c>
       <c r="J82" t="n">
-        <v>0.01764274358856231</v>
+        <v>0.8839935223088191</v>
       </c>
       <c r="K82" t="n">
-        <v>0.07057097435424924</v>
+        <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>-0.02199186429966986</v>
+        <v>-0.01476277185615057</v>
       </c>
       <c r="M82" t="n">
-        <v>-0.1236997597915897</v>
+        <v>-0.06852577388176932</v>
       </c>
       <c r="N82" t="n">
-        <v>-0.05792973816526732</v>
+        <v>-0.05938193128547058</v>
       </c>
       <c r="O82" t="n">
-        <v>0.0122823582436012</v>
+        <v>0.02924062339302871</v>
       </c>
       <c r="P82" t="n">
-        <v>0.2467552551312517</v>
+        <v>0.6341240624966311</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.987021020525007</v>
+        <v>1</v>
       </c>
       <c r="R82" t="b">
         <v>1</v>
@@ -6624,40 +6624,40 @@
         <v>96</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.06198632222943621</v>
+        <v>-0.01951070589124372</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.321200033449908</v>
+        <v>-0.07598690435976779</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.09910052149098715</v>
+        <v>-0.07034665165135202</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.02435851681419367</v>
+        <v>0.03187656736407376</v>
       </c>
       <c r="J83" t="n">
-        <v>0.002230042228047965</v>
+        <v>0.8473632790854616</v>
       </c>
       <c r="K83" t="n">
-        <v>0.01561029559633575</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>-0.06519875017464699</v>
+        <v>-0.06236120435516383</v>
       </c>
       <c r="M83" t="n">
-        <v>-0.3665120992061885</v>
+        <v>-0.2982063400607586</v>
       </c>
       <c r="N83" t="n">
-        <v>-0.1007384074020945</v>
+        <v>-0.1027344043976351</v>
       </c>
       <c r="O83" t="n">
-        <v>-0.02814126091499421</v>
+        <v>-0.02079729125041627</v>
       </c>
       <c r="P83" t="n">
-        <v>0.0003723367798351546</v>
+        <v>0.005560498432175352</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.002234020679010928</v>
+        <v>0.03336299059305212</v>
       </c>
       <c r="R83" t="b">
         <v>1</v>
@@ -6699,40 +6699,40 @@
         <v>96</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.05593113725369917</v>
+        <v>-0.03469874437634862</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.3093732097154723</v>
+        <v>-0.155418761185503</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.09191388723890419</v>
+        <v>-0.08055250991017629</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.02200316872016515</v>
+        <v>0.009824615277513014</v>
       </c>
       <c r="J84" t="n">
-        <v>0.003378349579121268</v>
+        <v>0.09314440642370184</v>
       </c>
       <c r="K84" t="n">
-        <v>0.02027009747472761</v>
+        <v>0.5588664385422111</v>
       </c>
       <c r="L84" t="n">
-        <v>-0.06744086563770194</v>
+        <v>-0.06385692951627549</v>
       </c>
       <c r="M84" t="n">
-        <v>-0.3729990632089324</v>
+        <v>-0.2976252073538662</v>
       </c>
       <c r="N84" t="n">
-        <v>-0.1037433691468437</v>
+        <v>-0.10750008530932</v>
       </c>
       <c r="O84" t="n">
-        <v>-0.03270807477986876</v>
+        <v>-0.0242504057551102</v>
       </c>
       <c r="P84" t="n">
-        <v>0.0005574574664504758</v>
+        <v>0.01035547633311089</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.002787287332252379</v>
+        <v>0.05177738166555447</v>
       </c>
       <c r="R84" t="b">
         <v>1</v>
@@ -6774,40 +6774,40 @@
         <v>96</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.09551724871039381</v>
+        <v>-0.1227277049611609</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.4547491972067882</v>
+        <v>-0.4256554804756513</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.136894540149313</v>
+        <v>-0.180654222370856</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.05563942003711406</v>
+        <v>-0.06730650072308478</v>
       </c>
       <c r="J85" t="n">
-        <v>8.366831181790742e-05</v>
+        <v>0.0002099939140949165</v>
       </c>
       <c r="K85" t="n">
-        <v>0.0007530148063611667</v>
+        <v>0.001889945226854248</v>
       </c>
       <c r="L85" t="n">
-        <v>-0.1233842281890366</v>
+        <v>-0.1102223363188731</v>
       </c>
       <c r="M85" t="n">
-        <v>-0.5431774267729212</v>
+        <v>-0.4308165051248014</v>
       </c>
       <c r="N85" t="n">
-        <v>-0.1666241941195683</v>
+        <v>-0.1613182082042176</v>
       </c>
       <c r="O85" t="n">
-        <v>-0.07993691789913736</v>
+        <v>-0.05985002204477696</v>
       </c>
       <c r="P85" t="n">
-        <v>2.184985238627574e-06</v>
+        <v>8.034905770325598e-05</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.966486714764816e-05</v>
+        <v>0.0006427924616260478</v>
       </c>
       <c r="R85" t="b">
         <v>1</v>
@@ -6849,40 +6849,40 @@
         <v>96</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.07050810974654612</v>
+        <v>-0.08492860647820306</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.3762457078948004</v>
+        <v>-0.3276407371722362</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.1071974235009379</v>
+        <v>-0.1361113082517874</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.03285103931979513</v>
+        <v>-0.03371070809350222</v>
       </c>
       <c r="J86" t="n">
-        <v>0.0002086058942940861</v>
+        <v>0.0004744613751133158</v>
       </c>
       <c r="K86" t="n">
-        <v>0.001668847154352689</v>
+        <v>0.00332122962579321</v>
       </c>
       <c r="L86" t="n">
-        <v>-0.08468486349678302</v>
+        <v>-0.1004372892659506</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.4376312604408</v>
+        <v>-0.4207408841902594</v>
       </c>
       <c r="N86" t="n">
-        <v>-0.1234792802506679</v>
+        <v>-0.1486909096292141</v>
       </c>
       <c r="O86" t="n">
-        <v>-0.04708473096198645</v>
+        <v>-0.0546921723904169</v>
       </c>
       <c r="P86" t="n">
-        <v>3.852088992531227e-05</v>
+        <v>1.283238814240124e-05</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.0003081671194024982</v>
+        <v>0.0001154914932816111</v>
       </c>
       <c r="R86" t="b">
         <v>1</v>
@@ -6924,40 +6924,40 @@
         <v>96</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.05551084284552787</v>
+        <v>-0.1007154002347985</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.2590497451907869</v>
+        <v>-0.3557927118072223</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.09673729776843155</v>
+        <v>-0.1561082789135046</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.01277193726013649</v>
+        <v>-0.04567646738124929</v>
       </c>
       <c r="J87" t="n">
-        <v>0.005328426876661392</v>
+        <v>0.0002789831766742497</v>
       </c>
       <c r="K87" t="n">
-        <v>0.02664213438330696</v>
+        <v>0.002231865413393998</v>
       </c>
       <c r="L87" t="n">
-        <v>-0.1035972044120012</v>
+        <v>-0.09942101801976322</v>
       </c>
       <c r="M87" t="n">
-        <v>-0.4540697335885744</v>
+        <v>-0.3415240041245218</v>
       </c>
       <c r="N87" t="n">
-        <v>-0.1490165731133218</v>
+        <v>-0.1579991800460256</v>
       </c>
       <c r="O87" t="n">
-        <v>-0.05908506636954828</v>
+        <v>-0.04106044532443877</v>
       </c>
       <c r="P87" t="n">
-        <v>5.036528267991708e-05</v>
+        <v>0.001272597980634811</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.0003525569787594196</v>
+        <v>0.008908185864443679</v>
       </c>
       <c r="R87" t="b">
         <v>1</v>
@@ -6999,40 +6999,40 @@
         <v>96</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.2490069806007559</v>
+        <v>-0.2654457479614382</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.9349047161042719</v>
+        <v>-0.7408051344993585</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.3026928711523947</v>
+        <v>-0.3380562944300051</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1983530755970293</v>
+        <v>-0.1949236790714499</v>
       </c>
       <c r="J88" t="n">
-        <v>2.387187035174395e-11</v>
+        <v>3.63114911716074e-09</v>
       </c>
       <c r="K88" t="n">
-        <v>2.625905738691835e-10</v>
+        <v>3.994264028876814e-08</v>
       </c>
       <c r="L88" t="n">
-        <v>-0.2909147288571989</v>
+        <v>-0.2835152430896516</v>
       </c>
       <c r="M88" t="n">
-        <v>-1.045143388007517</v>
+        <v>-0.8427747078791746</v>
       </c>
       <c r="N88" t="n">
-        <v>-0.3466955826457034</v>
+        <v>-0.3521755642516363</v>
       </c>
       <c r="O88" t="n">
-        <v>-0.2374383422667307</v>
+        <v>-0.2161780527135286</v>
       </c>
       <c r="P88" t="n">
-        <v>3.633452787227257e-13</v>
+        <v>1.968599963046453e-10</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.996798065949983e-12</v>
+        <v>2.165459959351098e-09</v>
       </c>
       <c r="R88" t="b">
         <v>1</v>
@@ -7074,40 +7074,40 @@
         <v>96</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.1109469135015137</v>
+        <v>-0.1495163128541086</v>
       </c>
       <c r="G89" t="n">
-        <v>-0.5162193658619101</v>
+        <v>-0.5149386736803846</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.1529022431325116</v>
+        <v>-0.2072018653052111</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0724859734091898</v>
+        <v>-0.09471214327737069</v>
       </c>
       <c r="J89" t="n">
-        <v>1.933530861947346e-06</v>
+        <v>2.054706219721777e-06</v>
       </c>
       <c r="K89" t="n">
-        <v>1.933530861947347e-05</v>
+        <v>2.054706219721777e-05</v>
       </c>
       <c r="L89" t="n">
-        <v>-0.11272903205469</v>
+        <v>-0.1571935096881464</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.5629694283363904</v>
+        <v>-0.635827310781476</v>
       </c>
       <c r="N89" t="n">
-        <v>-0.1524614133315819</v>
+        <v>-0.20731393871445</v>
       </c>
       <c r="O89" t="n">
-        <v>-0.07535618275030284</v>
+        <v>-0.1106166616661781</v>
       </c>
       <c r="P89" t="n">
-        <v>5.104343425059778e-07</v>
+        <v>4.489583790122852e-08</v>
       </c>
       <c r="Q89" t="n">
-        <v>5.104343425059778e-06</v>
+        <v>4.489583790122852e-07</v>
       </c>
       <c r="R89" t="b">
         <v>1</v>
@@ -13749,37 +13749,37 @@
         <v>96</v>
       </c>
       <c r="F178" t="n">
-        <v>0.007368635319013485</v>
+        <v>-0.004133545306776898</v>
       </c>
       <c r="G178" t="n">
-        <v>0.03796598615815393</v>
+        <v>-0.01944111275093433</v>
       </c>
       <c r="H178" t="n">
-        <v>-0.03234846887970153</v>
+        <v>-0.04491294559521535</v>
       </c>
       <c r="I178" t="n">
-        <v>0.04922882355084809</v>
+        <v>0.04003314841132631</v>
       </c>
       <c r="J178" t="n">
-        <v>0.8922643965120693</v>
+        <v>0.760367259464929</v>
       </c>
       <c r="K178" t="n">
         <v>1</v>
       </c>
       <c r="L178" t="n">
-        <v>-0.003287313053674187</v>
+        <v>0.002061029451715037</v>
       </c>
       <c r="M178" t="n">
-        <v>-0.01728704672941865</v>
+        <v>0.009243110367279629</v>
       </c>
       <c r="N178" t="n">
-        <v>-0.04016203177236086</v>
+        <v>-0.04683460071171345</v>
       </c>
       <c r="O178" t="n">
-        <v>0.03570467692039141</v>
+        <v>0.04977570531609515</v>
       </c>
       <c r="P178" t="n">
-        <v>0.8259308256740822</v>
+        <v>0.642499350355514</v>
       </c>
       <c r="Q178" t="n">
         <v>1</v>
@@ -13792,12 +13792,12 @@
       </c>
       <c r="T178" t="inlineStr">
         <is>
+          <t>K5</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
           <t>K0</t>
-        </is>
-      </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>K5</t>
         </is>
       </c>
     </row>
@@ -13824,37 +13824,37 @@
         <v>96</v>
       </c>
       <c r="F179" t="n">
-        <v>-0.02736595964660181</v>
+        <v>-0.02004403461751776</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.1142210169194071</v>
+        <v>-0.06993634481606276</v>
       </c>
       <c r="H179" t="n">
-        <v>-0.07514260582595247</v>
+        <v>-0.07639967386853271</v>
       </c>
       <c r="I179" t="n">
-        <v>0.02190658897161575</v>
+        <v>0.03823122803635241</v>
       </c>
       <c r="J179" t="n">
-        <v>0.1821435855646644</v>
+        <v>0.6106688053718941</v>
       </c>
       <c r="K179" t="n">
         <v>1</v>
       </c>
       <c r="L179" t="n">
-        <v>-0.03008293155387734</v>
+        <v>-0.03786230727207434</v>
       </c>
       <c r="M179" t="n">
-        <v>-0.1435028178849962</v>
+        <v>-0.1445223704951877</v>
       </c>
       <c r="N179" t="n">
-        <v>-0.07321418741948428</v>
+        <v>-0.09398463649579256</v>
       </c>
       <c r="O179" t="n">
-        <v>0.01254165441459111</v>
+        <v>0.01409398392128226</v>
       </c>
       <c r="P179" t="n">
-        <v>0.2369961371186001</v>
+        <v>0.1827417047158065</v>
       </c>
       <c r="Q179" t="n">
         <v>1</v>
@@ -13899,37 +13899,37 @@
         <v>96</v>
       </c>
       <c r="F180" t="n">
-        <v>-0.003480630974710346</v>
+        <v>0.01997311276027918</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.01534494310787654</v>
+        <v>0.07142428568507096</v>
       </c>
       <c r="H180" t="n">
-        <v>-0.04821093876966422</v>
+        <v>-0.03788329412555155</v>
       </c>
       <c r="I180" t="n">
-        <v>0.04275630065082583</v>
+        <v>0.07746190836324228</v>
       </c>
       <c r="J180" t="n">
-        <v>0.6376052509636516</v>
+        <v>0.599563378073052</v>
       </c>
       <c r="K180" t="n">
         <v>1</v>
       </c>
       <c r="L180" t="n">
-        <v>-0.01494358718817975</v>
+        <v>0.009370932166406524</v>
       </c>
       <c r="M180" t="n">
-        <v>-0.06697887745326286</v>
+        <v>0.03488768530872764</v>
       </c>
       <c r="N180" t="n">
-        <v>-0.05954796629695963</v>
+        <v>-0.04568209167464848</v>
       </c>
       <c r="O180" t="n">
-        <v>0.03112473579375089</v>
+        <v>0.06290519778599654</v>
       </c>
       <c r="P180" t="n">
-        <v>0.3709966131595706</v>
+        <v>0.9120721947286768</v>
       </c>
       <c r="Q180" t="n">
         <v>1</v>
@@ -13942,12 +13942,12 @@
       </c>
       <c r="T180" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K0</t>
         </is>
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K0</t>
         </is>
       </c>
     </row>
@@ -13974,50 +13974,50 @@
         <v>96</v>
       </c>
       <c r="F181" t="n">
-        <v>0.002132966412258302</v>
+        <v>-0.0059592413430939</v>
       </c>
       <c r="G181" t="n">
-        <v>0.009607508926497619</v>
+        <v>-0.02176476327603758</v>
       </c>
       <c r="H181" t="n">
-        <v>-0.04242159982056128</v>
+        <v>-0.06057055084636476</v>
       </c>
       <c r="I181" t="n">
-        <v>0.0462653143315865</v>
+        <v>0.04823434551492429</v>
       </c>
       <c r="J181" t="n">
-        <v>0.8643080142489131</v>
+        <v>0.5932705914264838</v>
       </c>
       <c r="K181" t="n">
         <v>1</v>
       </c>
       <c r="L181" t="n">
-        <v>-0.009925130504584758</v>
+        <v>-0.001732861155938078</v>
       </c>
       <c r="M181" t="n">
-        <v>-0.04296722558181825</v>
+        <v>-0.00680061724225333</v>
       </c>
       <c r="N181" t="n">
-        <v>-0.05699554015073222</v>
+        <v>-0.0528080446919434</v>
       </c>
       <c r="O181" t="n">
-        <v>0.03822477445286783</v>
+        <v>0.05288492073104464</v>
       </c>
       <c r="P181" t="n">
-        <v>0.6166632111549522</v>
+        <v>0.6257051721049932</v>
       </c>
       <c r="Q181" t="n">
         <v>1</v>
       </c>
       <c r="R181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S181" t="b">
         <v>0</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
-          <t>K0</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="U181" t="inlineStr">
@@ -14049,46 +14049,46 @@
         <v>96</v>
       </c>
       <c r="F182" t="n">
-        <v>-0.01858161142937232</v>
+        <v>-0.01470906886727699</v>
       </c>
       <c r="G182" t="n">
-        <v>-0.09664617558932308</v>
+        <v>-0.06345402319554223</v>
       </c>
       <c r="H182" t="n">
-        <v>-0.05722161339918951</v>
+        <v>-0.05979171166139677</v>
       </c>
       <c r="I182" t="n">
-        <v>0.01983346253325226</v>
+        <v>0.03178187138519218</v>
       </c>
       <c r="J182" t="n">
-        <v>0.1051363913346376</v>
+        <v>0.4386941477641001</v>
       </c>
       <c r="K182" t="n">
         <v>1</v>
       </c>
       <c r="L182" t="n">
-        <v>-0.04663433736527777</v>
+        <v>-0.01576558650199873</v>
       </c>
       <c r="M182" t="n">
-        <v>-0.2789294434644485</v>
+        <v>-0.07673386448071109</v>
       </c>
       <c r="N182" t="n">
-        <v>-0.07899729843125498</v>
+        <v>-0.06067150815767287</v>
       </c>
       <c r="O182" t="n">
-        <v>-0.01512259572875383</v>
+        <v>0.0245173195592053</v>
       </c>
       <c r="P182" t="n">
-        <v>0.004122810940203924</v>
+        <v>0.4117321025927735</v>
       </c>
       <c r="Q182" t="n">
-        <v>0.04122810940203925</v>
+        <v>1</v>
       </c>
       <c r="R182" t="b">
         <v>1</v>
       </c>
       <c r="S182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -14124,46 +14124,46 @@
         <v>96</v>
       </c>
       <c r="F183" t="n">
-        <v>-0.02004013099361565</v>
+        <v>-0.02882407618790166</v>
       </c>
       <c r="G183" t="n">
-        <v>-0.1054909900405642</v>
+        <v>-0.1174776149249416</v>
       </c>
       <c r="H183" t="n">
-        <v>-0.05896133481791252</v>
+        <v>-0.07720374359347368</v>
       </c>
       <c r="I183" t="n">
-        <v>0.01659678369015821</v>
+        <v>0.01867290528354405</v>
       </c>
       <c r="J183" t="n">
-        <v>0.7151680306708604</v>
+        <v>0.6126890760182544</v>
       </c>
       <c r="K183" t="n">
         <v>1</v>
       </c>
       <c r="L183" t="n">
-        <v>-0.04654066228370685</v>
+        <v>-0.02457680256758405</v>
       </c>
       <c r="M183" t="n">
-        <v>-0.2236186890153221</v>
+        <v>-0.1010012493868563</v>
       </c>
       <c r="N183" t="n">
-        <v>-0.0884018146163526</v>
+        <v>-0.0753245172610645</v>
       </c>
       <c r="O183" t="n">
-        <v>-0.006683221763602499</v>
+        <v>0.02375971548625378</v>
       </c>
       <c r="P183" t="n">
-        <v>0.04981991613023073</v>
+        <v>0.6686169273680718</v>
       </c>
       <c r="Q183" t="n">
-        <v>0.4483792451720766</v>
+        <v>1</v>
       </c>
       <c r="R183" t="b">
         <v>1</v>
       </c>
       <c r="S183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -14199,43 +14199,43 @@
         <v>96</v>
       </c>
       <c r="F184" t="n">
-        <v>0.006185831912923379</v>
+        <v>0.01795073678596023</v>
       </c>
       <c r="G184" t="n">
-        <v>0.03676768670880912</v>
+        <v>0.07260819926857796</v>
       </c>
       <c r="H184" t="n">
-        <v>-0.02485837711126434</v>
+        <v>-0.02961427169724626</v>
       </c>
       <c r="I184" t="n">
-        <v>0.04054641931142331</v>
+        <v>0.06421240449569721</v>
       </c>
       <c r="J184" t="n">
-        <v>0.962091363719499</v>
+        <v>0.5015081670375793</v>
       </c>
       <c r="K184" t="n">
         <v>1</v>
       </c>
       <c r="L184" t="n">
-        <v>-0.00282633683610851</v>
+        <v>0.008332880047583591</v>
       </c>
       <c r="M184" t="n">
-        <v>-0.01755606751569509</v>
+        <v>0.04160124582781038</v>
       </c>
       <c r="N184" t="n">
-        <v>-0.03487421340556016</v>
+        <v>-0.03183569210294784</v>
       </c>
       <c r="O184" t="n">
-        <v>0.02786420774411775</v>
+        <v>0.04922566225355475</v>
       </c>
       <c r="P184" t="n">
-        <v>0.9223971464320886</v>
+        <v>0.6039344476991214</v>
       </c>
       <c r="Q184" t="n">
         <v>1</v>
       </c>
       <c r="R184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S184" t="b">
         <v>0</v>
@@ -14247,7 +14247,7 @@
       </c>
       <c r="U184" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K0</t>
         </is>
       </c>
     </row>
@@ -14274,37 +14274,37 @@
         <v>96</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.02003768007851457</v>
+        <v>-0.004810296530739639</v>
       </c>
       <c r="G185" t="n">
-        <v>-0.07961107757935917</v>
+        <v>-0.01912473874274128</v>
       </c>
       <c r="H185" t="n">
-        <v>-0.07081807789031355</v>
+        <v>-0.05537913716865922</v>
       </c>
       <c r="I185" t="n">
-        <v>0.03030552871111064</v>
+        <v>0.04354780169167378</v>
       </c>
       <c r="J185" t="n">
-        <v>0.21411251948631</v>
+        <v>0.7930218917720896</v>
       </c>
       <c r="K185" t="n">
         <v>1</v>
       </c>
       <c r="L185" t="n">
-        <v>-0.03078254206592055</v>
+        <v>-0.0188306090418757</v>
       </c>
       <c r="M185" t="n">
-        <v>-0.1313841540929931</v>
+        <v>-0.07017554645098049</v>
       </c>
       <c r="N185" t="n">
-        <v>-0.07820470305685816</v>
+        <v>-0.07273557682240885</v>
       </c>
       <c r="O185" t="n">
-        <v>0.01437143546427844</v>
+        <v>0.03534116075235843</v>
       </c>
       <c r="P185" t="n">
-        <v>0.1906820219436359</v>
+        <v>0.3788985750003142</v>
       </c>
       <c r="Q185" t="n">
         <v>1</v>
@@ -14349,37 +14349,37 @@
         <v>96</v>
       </c>
       <c r="F186" t="n">
-        <v>-0.01480512930867958</v>
+        <v>-0.01215449562629954</v>
       </c>
       <c r="G186" t="n">
-        <v>-0.08496130999021627</v>
+        <v>-0.05374566432267474</v>
       </c>
       <c r="H186" t="n">
-        <v>-0.05160944286738262</v>
+        <v>-0.05752643956478644</v>
       </c>
       <c r="I186" t="n">
-        <v>0.01660060015281633</v>
+        <v>0.0317572612294211</v>
       </c>
       <c r="J186" t="n">
-        <v>0.5225092021027675</v>
+        <v>0.5692905230226141</v>
       </c>
       <c r="K186" t="n">
         <v>1</v>
       </c>
       <c r="L186" t="n">
-        <v>-0.02512857186207612</v>
+        <v>-0.02867061718698884</v>
       </c>
       <c r="M186" t="n">
-        <v>-0.1374049221117012</v>
+        <v>-0.1580408482546369</v>
       </c>
       <c r="N186" t="n">
-        <v>-0.06221516297778874</v>
+        <v>-0.06690442877340902</v>
       </c>
       <c r="O186" t="n">
-        <v>0.009469322145647592</v>
+        <v>0.004885119898295924</v>
       </c>
       <c r="P186" t="n">
-        <v>0.2813473505182984</v>
+        <v>0.2346402238261874</v>
       </c>
       <c r="Q186" t="n">
         <v>1</v>
@@ -14424,50 +14424,50 @@
         <v>96</v>
       </c>
       <c r="F187" t="n">
-        <v>0.01773071499933712</v>
+        <v>-0.006594885279337677</v>
       </c>
       <c r="G187" t="n">
-        <v>0.08358150828142689</v>
+        <v>-0.03050450431656056</v>
       </c>
       <c r="H187" t="n">
-        <v>-0.0231958252885163</v>
+        <v>-0.04889213692054491</v>
       </c>
       <c r="I187" t="n">
-        <v>0.0613736582573998</v>
+        <v>0.0353681309709632</v>
       </c>
       <c r="J187" t="n">
-        <v>0.9342371845459214</v>
+        <v>0.6083164761632893</v>
       </c>
       <c r="K187" t="n">
         <v>1</v>
       </c>
       <c r="L187" t="n">
-        <v>-0.02212923749527558</v>
+        <v>-0.01621172325943092</v>
       </c>
       <c r="M187" t="n">
-        <v>-0.1016282874374634</v>
+        <v>-0.08090857266398199</v>
       </c>
       <c r="N187" t="n">
-        <v>-0.06529363940840373</v>
+        <v>-0.054183997518439</v>
       </c>
       <c r="O187" t="n">
-        <v>0.01812382156121244</v>
+        <v>0.02153163921077347</v>
       </c>
       <c r="P187" t="n">
-        <v>0.1378750891888599</v>
+        <v>0.3053781740874427</v>
       </c>
       <c r="Q187" t="n">
         <v>1</v>
       </c>
       <c r="R187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S187" t="b">
         <v>0</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>K0</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="U187" t="inlineStr">
@@ -14499,40 +14499,40 @@
         <v>96</v>
       </c>
       <c r="F188" t="n">
-        <v>-0.007653542203058877</v>
+        <v>-0.06116497797080228</v>
       </c>
       <c r="G188" t="n">
-        <v>-0.04353172037239663</v>
+        <v>-0.2961761893748623</v>
       </c>
       <c r="H188" t="n">
-        <v>-0.04255333276074155</v>
+        <v>-0.09990408040567678</v>
       </c>
       <c r="I188" t="n">
-        <v>0.03013176673910656</v>
+        <v>-0.02058408140702435</v>
       </c>
       <c r="J188" t="n">
-        <v>0.2679143352247111</v>
+        <v>0.001140056544204435</v>
       </c>
       <c r="K188" t="n">
-        <v>1</v>
+        <v>0.01254062198624878</v>
       </c>
       <c r="L188" t="n">
-        <v>-0.05134661039960375</v>
+        <v>-0.06627546487453609</v>
       </c>
       <c r="M188" t="n">
-        <v>-0.2528897685169886</v>
+        <v>-0.3121508558027484</v>
       </c>
       <c r="N188" t="n">
-        <v>-0.08973307472296863</v>
+        <v>-0.1060325069400933</v>
       </c>
       <c r="O188" t="n">
-        <v>-0.007950840549637904</v>
+        <v>-0.02402915695272511</v>
       </c>
       <c r="P188" t="n">
-        <v>0.002765486676363738</v>
+        <v>0.001594553835352257</v>
       </c>
       <c r="Q188" t="n">
-        <v>0.03042035344000112</v>
+        <v>0.01754009218887483</v>
       </c>
       <c r="R188" t="b">
         <v>1</v>
@@ -15432,10 +15432,10 @@
         <v>198</v>
       </c>
       <c r="D2" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E2" t="n">
-        <v>79.8</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="3">
@@ -15450,10 +15450,10 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D3" t="n">
         <v>76</v>
-      </c>
-      <c r="D3" t="n">
-        <v>74</v>
       </c>
       <c r="E3" t="n">
         <v>97.40000000000001</v>
@@ -15471,10 +15471,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" t="n">
         <v>100</v>
@@ -15513,13 +15513,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D6" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E6" t="n">
-        <v>96.7</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -15534,10 +15534,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" t="n">
         <v>98.2</v>
@@ -15555,13 +15555,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D8" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E8" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9">
@@ -15576,10 +15576,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" t="n">
         <v>100</v>
@@ -15600,10 +15600,10 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E10" t="n">
-        <v>80.59999999999999</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="11">
@@ -15621,10 +15621,10 @@
         <v>99</v>
       </c>
       <c r="D11" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>70.7</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="12">
@@ -15699,13 +15699,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E15" t="n">
-        <v>91.2</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -15720,10 +15720,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>100</v>
@@ -15741,13 +15741,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>91.3</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -15762,10 +15762,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>100</v>
@@ -15786,10 +15786,10 @@
         <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E19" t="n">
-        <v>72.2</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -15807,10 +15807,10 @@
         <v>99</v>
       </c>
       <c r="D20" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E20" t="n">
-        <v>88.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -15825,13 +15825,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D21" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E21" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="22">
@@ -15846,10 +15846,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E22" t="n">
         <v>100</v>
@@ -15909,13 +15909,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>98</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -15930,10 +15930,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D26" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E26" t="n">
         <v>100</v>
@@ -15951,10 +15951,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D27" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E27" t="n">
         <v>100</v>
@@ -15975,10 +15975,10 @@
         <v>90</v>
       </c>
       <c r="D28" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E28" t="n">
-        <v>88.90000000000001</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="29">
@@ -17319,10 +17319,10 @@
         <v>22</v>
       </c>
       <c r="D92" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E92" t="n">
-        <v>81.8</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -17337,10 +17337,10 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E93" t="n">
         <v>100</v>
@@ -17358,10 +17358,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="95">
@@ -17394,10 +17397,10 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D96" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E96" t="n">
         <v>100</v>
@@ -17415,10 +17418,10 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D97" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E97" t="n">
         <v>100</v>
@@ -17436,10 +17439,10 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D98" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E98" t="n">
         <v>100</v>
@@ -17457,10 +17460,10 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D99" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E99" t="n">
         <v>100</v>
@@ -17481,10 +17484,10 @@
         <v>20</v>
       </c>
       <c r="D100" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E100" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="101">
@@ -22320,16 +22323,16 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.002</v>
+        <v>0.006</v>
       </c>
       <c r="K79" t="n">
-        <v>0.006</v>
+        <v>0.019</v>
       </c>
       <c r="O79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P79" t="n">
         <v>0.05</v>
@@ -22371,16 +22374,16 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>0.019</v>
+        <v>0.007</v>
       </c>
       <c r="O80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P80" t="n">
         <v>0.05</v>
@@ -22422,13 +22425,22 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J81" t="n">
-        <v>0.014</v>
+        <v>0.068</v>
       </c>
       <c r="K81" t="n">
-        <v>0.033</v>
+        <v>0.043</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1.148</v>
       </c>
       <c r="O81" t="b">
         <v>1</v>
@@ -22473,22 +22485,22 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J82" t="n">
-        <v>0.055</v>
+        <v>0.107</v>
       </c>
       <c r="K82" t="n">
-        <v>0.081</v>
+        <v>0.098</v>
       </c>
       <c r="L82" t="n">
-        <v>1.472</v>
+        <v>0.914</v>
       </c>
       <c r="M82" t="n">
-        <v>1.027</v>
+        <v>0.641</v>
       </c>
       <c r="N82" t="n">
-        <v>1.774</v>
+        <v>1.256</v>
       </c>
       <c r="O82" t="b">
         <v>1</v>
@@ -22533,22 +22545,22 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J83" t="n">
-        <v>0.063</v>
+        <v>0.106</v>
       </c>
       <c r="K83" t="n">
-        <v>0.066</v>
+        <v>0.074</v>
       </c>
       <c r="L83" t="n">
-        <v>1.042</v>
+        <v>0.701</v>
       </c>
       <c r="M83" t="n">
-        <v>0.706</v>
+        <v>0.34</v>
       </c>
       <c r="N83" t="n">
-        <v>1.378</v>
+        <v>1.039</v>
       </c>
       <c r="O83" t="b">
         <v>1</v>
@@ -22593,13 +22605,22 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J84" t="n">
-        <v>0.033</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>0.035</v>
+        <v>0.05</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="N84" t="n">
+        <v>1.034</v>
       </c>
       <c r="O84" t="b">
         <v>1</v>
@@ -22644,13 +22665,22 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J85" t="n">
-        <v>0.041</v>
+        <v>0.053</v>
       </c>
       <c r="K85" t="n">
-        <v>0.034</v>
+        <v>0.063</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1.195</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="N85" t="n">
+        <v>1.671</v>
       </c>
       <c r="O85" t="b">
         <v>1</v>
@@ -22695,22 +22725,22 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J86" t="n">
-        <v>0.062</v>
+        <v>0.082</v>
       </c>
       <c r="K86" t="n">
-        <v>0.063</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>1.027</v>
+        <v>0.88</v>
       </c>
       <c r="M86" t="n">
-        <v>0.694</v>
+        <v>0.489</v>
       </c>
       <c r="N86" t="n">
-        <v>1.356</v>
+        <v>1.362</v>
       </c>
       <c r="O86" t="b">
         <v>1</v>
@@ -22755,22 +22785,22 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J87" t="n">
-        <v>0.083</v>
+        <v>0.077</v>
       </c>
       <c r="K87" t="n">
-        <v>0.076</v>
+        <v>0.095</v>
       </c>
       <c r="L87" t="n">
-        <v>0.919</v>
+        <v>1.23</v>
       </c>
       <c r="M87" t="n">
-        <v>0.631</v>
+        <v>0.652</v>
       </c>
       <c r="N87" t="n">
-        <v>1.268</v>
+        <v>1.971</v>
       </c>
       <c r="O87" t="b">
         <v>1</v>
@@ -22815,13 +22845,13 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.039</v>
+        <v>-0.023</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.056</v>
+        <v>-0.041</v>
       </c>
       <c r="O88" t="b">
         <v>1</v>
@@ -22866,22 +22896,22 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J89" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="K89" t="n">
-        <v>0.093</v>
+        <v>0.079</v>
       </c>
       <c r="L89" t="n">
-        <v>1.085</v>
+        <v>0.968</v>
       </c>
       <c r="M89" t="n">
-        <v>0.823</v>
+        <v>0.497</v>
       </c>
       <c r="N89" t="n">
-        <v>1.442</v>
+        <v>1.525</v>
       </c>
       <c r="O89" t="b">
         <v>1</v>
@@ -23193,10 +23223,10 @@
         <v>4.125</v>
       </c>
       <c r="M95" t="n">
-        <v>2.372</v>
+        <v>2.407</v>
       </c>
       <c r="N95" t="n">
-        <v>5.269</v>
+        <v>5.335</v>
       </c>
       <c r="O95" t="b">
         <v>1</v>
@@ -23304,10 +23334,10 @@
         <v>5.122</v>
       </c>
       <c r="M97" t="n">
-        <v>2.411</v>
+        <v>2.391</v>
       </c>
       <c r="N97" t="n">
-        <v>6.085</v>
+        <v>6.108</v>
       </c>
       <c r="O97" t="b">
         <v>1</v>
@@ -23364,10 +23394,10 @@
         <v>1.659</v>
       </c>
       <c r="M98" t="n">
-        <v>1.368</v>
+        <v>1.38</v>
       </c>
       <c r="N98" t="n">
-        <v>2.04</v>
+        <v>2.044</v>
       </c>
       <c r="O98" t="b">
         <v>1</v>
@@ -23424,10 +23454,10 @@
         <v>2.421</v>
       </c>
       <c r="M99" t="n">
-        <v>1.752</v>
+        <v>1.714</v>
       </c>
       <c r="N99" t="n">
-        <v>3.792</v>
+        <v>3.975</v>
       </c>
       <c r="O99" t="b">
         <v>1</v>
@@ -23484,7 +23514,7 @@
         <v>1.098</v>
       </c>
       <c r="M100" t="n">
-        <v>0.962</v>
+        <v>0.966</v>
       </c>
       <c r="N100" t="n">
         <v>1.252</v>
@@ -27678,13 +27708,13 @@
         <v>1</v>
       </c>
       <c r="I171" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J171" t="n">
-        <v>-0.007</v>
+        <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>0.013</v>
+        <v>-0.014</v>
       </c>
       <c r="O171" t="b">
         <v>0</v>
@@ -27732,10 +27762,19 @@
         <v>96</v>
       </c>
       <c r="J172" t="n">
-        <v>0.016</v>
+        <v>0.06</v>
       </c>
       <c r="K172" t="n">
-        <v>0.027</v>
+        <v>0.023</v>
+      </c>
+      <c r="L172" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="M172" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="N172" t="n">
+        <v>0.8129999999999999</v>
       </c>
       <c r="O172" t="b">
         <v>1</v>
@@ -27780,22 +27819,22 @@
         <v>1</v>
       </c>
       <c r="I173" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J173" t="n">
-        <v>0.056</v>
+        <v>0.097</v>
       </c>
       <c r="K173" t="n">
-        <v>0.075</v>
+        <v>0.081</v>
       </c>
       <c r="L173" t="n">
-        <v>1.326</v>
+        <v>0.833</v>
       </c>
       <c r="M173" t="n">
-        <v>0.925</v>
+        <v>0.51</v>
       </c>
       <c r="N173" t="n">
-        <v>1.608</v>
+        <v>1.122</v>
       </c>
       <c r="O173" t="b">
         <v>1</v>
@@ -27843,19 +27882,19 @@
         <v>96</v>
       </c>
       <c r="J174" t="n">
-        <v>0.065</v>
+        <v>0.099</v>
       </c>
       <c r="K174" t="n">
-        <v>0.06</v>
+        <v>0.052</v>
       </c>
       <c r="L174" t="n">
-        <v>0.925</v>
+        <v>0.529</v>
       </c>
       <c r="M174" t="n">
-        <v>0.627</v>
+        <v>0.172</v>
       </c>
       <c r="N174" t="n">
-        <v>1.268</v>
+        <v>0.804</v>
       </c>
       <c r="O174" t="b">
         <v>1</v>
@@ -27903,10 +27942,19 @@
         <v>96</v>
       </c>
       <c r="J175" t="n">
-        <v>0.035</v>
+        <v>0.074</v>
       </c>
       <c r="K175" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="M175" t="n">
+        <v>-0.08500000000000001</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0.789</v>
       </c>
       <c r="O175" t="b">
         <v>1</v>
@@ -27954,10 +28002,10 @@
         <v>96</v>
       </c>
       <c r="J176" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="K176" t="n">
-        <v>0.028</v>
+        <v>0.038</v>
       </c>
       <c r="O176" t="b">
         <v>1</v>
@@ -28005,19 +28053,19 @@
         <v>96</v>
       </c>
       <c r="J177" t="n">
-        <v>0.063</v>
+        <v>0.074</v>
       </c>
       <c r="K177" t="n">
-        <v>0.058</v>
+        <v>0.052</v>
       </c>
       <c r="L177" t="n">
-        <v>0.908</v>
+        <v>0.705</v>
       </c>
       <c r="M177" t="n">
-        <v>0.576</v>
+        <v>0.272</v>
       </c>
       <c r="N177" t="n">
-        <v>1.249</v>
+        <v>1.117</v>
       </c>
       <c r="O177" t="b">
         <v>1</v>
@@ -28065,19 +28113,19 @@
         <v>96</v>
       </c>
       <c r="J178" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K178" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="L178" t="n">
-        <v>0.832</v>
+        <v>1.073</v>
       </c>
       <c r="M178" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="N178" t="n">
-        <v>1.116</v>
+        <v>1.601</v>
       </c>
       <c r="O178" t="b">
         <v>1</v>
@@ -28125,10 +28173,10 @@
         <v>96</v>
       </c>
       <c r="J179" t="n">
-        <v>-0.037</v>
+        <v>-0.035</v>
       </c>
       <c r="K179" t="n">
-        <v>-0.062</v>
+        <v>-0.066</v>
       </c>
       <c r="O179" t="b">
         <v>1</v>
@@ -28176,19 +28224,19 @@
         <v>96</v>
       </c>
       <c r="J180" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="K180" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.057</v>
       </c>
       <c r="L180" t="n">
-        <v>0.997</v>
+        <v>0.748</v>
       </c>
       <c r="M180" t="n">
-        <v>0.755</v>
+        <v>0.337</v>
       </c>
       <c r="N180" t="n">
-        <v>1.299</v>
+        <v>1.175</v>
       </c>
       <c r="O180" t="b">
         <v>1</v>
@@ -28449,10 +28497,10 @@
         <v>3.713</v>
       </c>
       <c r="M185" t="n">
-        <v>2.183</v>
+        <v>2.113</v>
       </c>
       <c r="N185" t="n">
-        <v>5.057</v>
+        <v>5.127</v>
       </c>
       <c r="O185" t="b">
         <v>1</v>
@@ -28560,10 +28608,10 @@
         <v>4.626</v>
       </c>
       <c r="M187" t="n">
-        <v>2.278</v>
+        <v>2.334</v>
       </c>
       <c r="N187" t="n">
-        <v>5.846</v>
+        <v>5.741</v>
       </c>
       <c r="O187" t="b">
         <v>1</v>
@@ -28620,10 +28668,10 @@
         <v>1.589</v>
       </c>
       <c r="M188" t="n">
-        <v>1.297</v>
+        <v>1.293</v>
       </c>
       <c r="N188" t="n">
-        <v>2</v>
+        <v>1.978</v>
       </c>
       <c r="O188" t="b">
         <v>1</v>
@@ -28680,10 +28728,10 @@
         <v>2.247</v>
       </c>
       <c r="M189" t="n">
-        <v>1.557</v>
+        <v>1.552</v>
       </c>
       <c r="N189" t="n">
-        <v>3.748</v>
+        <v>3.981</v>
       </c>
       <c r="O189" t="b">
         <v>1</v>
@@ -28743,7 +28791,7 @@
         <v>0.944</v>
       </c>
       <c r="N190" t="n">
-        <v>1.21</v>
+        <v>1.208</v>
       </c>
       <c r="O190" t="b">
         <v>1</v>
@@ -33312,10 +33360,10 @@
         <v>96</v>
       </c>
       <c r="J268" t="n">
-        <v>0.016</v>
+        <v>0.031</v>
       </c>
       <c r="K268" t="n">
-        <v>0.019</v>
+        <v>0.046</v>
       </c>
       <c r="O268" t="b">
         <v>1</v>
@@ -33360,13 +33408,13 @@
         <v>0</v>
       </c>
       <c r="I269" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J269" t="n">
-        <v>0.01</v>
+        <v>0.033</v>
       </c>
       <c r="K269" t="n">
-        <v>0.032</v>
+        <v>0.036</v>
       </c>
       <c r="O269" t="b">
         <v>1</v>
@@ -33414,10 +33462,19 @@
         <v>96</v>
       </c>
       <c r="J270" t="n">
-        <v>0.032</v>
+        <v>0.091</v>
       </c>
       <c r="K270" t="n">
-        <v>0.046</v>
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="L270" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="M270" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="N270" t="n">
+        <v>1.121</v>
       </c>
       <c r="O270" t="b">
         <v>1</v>
@@ -33462,22 +33519,22 @@
         <v>0</v>
       </c>
       <c r="I271" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J271" t="n">
-        <v>0.073</v>
+        <v>0.128</v>
       </c>
       <c r="K271" t="n">
-        <v>0.094</v>
+        <v>0.126</v>
       </c>
       <c r="L271" t="n">
-        <v>1.29</v>
+        <v>0.987</v>
       </c>
       <c r="M271" t="n">
-        <v>0.964</v>
+        <v>0.75</v>
       </c>
       <c r="N271" t="n">
-        <v>1.678</v>
+        <v>1.314</v>
       </c>
       <c r="O271" t="b">
         <v>1</v>
@@ -33525,19 +33582,19 @@
         <v>96</v>
       </c>
       <c r="J272" t="n">
-        <v>0.081</v>
+        <v>0.13</v>
       </c>
       <c r="K272" t="n">
-        <v>0.079</v>
+        <v>0.098</v>
       </c>
       <c r="L272" t="n">
-        <v>0.974</v>
+        <v>0.757</v>
       </c>
       <c r="M272" t="n">
-        <v>0.696</v>
+        <v>0.548</v>
       </c>
       <c r="N272" t="n">
-        <v>1.269</v>
+        <v>0.991</v>
       </c>
       <c r="O272" t="b">
         <v>1</v>
@@ -33585,19 +33642,19 @@
         <v>96</v>
       </c>
       <c r="J273" t="n">
-        <v>0.052</v>
+        <v>0.105</v>
       </c>
       <c r="K273" t="n">
-        <v>0.048</v>
+        <v>0.074</v>
       </c>
       <c r="L273" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="M273" t="n">
-        <v>0.556</v>
+        <v>0.378</v>
       </c>
       <c r="N273" t="n">
-        <v>1.273</v>
+        <v>1.103</v>
       </c>
       <c r="O273" t="b">
         <v>1</v>
@@ -33645,19 +33702,19 @@
         <v>96</v>
       </c>
       <c r="J274" t="n">
-        <v>0.059</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="K274" t="n">
-        <v>0.048</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L274" t="n">
-        <v>0.8080000000000001</v>
+        <v>1.164</v>
       </c>
       <c r="M274" t="n">
-        <v>0.443</v>
+        <v>0.737</v>
       </c>
       <c r="N274" t="n">
-        <v>1.157</v>
+        <v>1.653</v>
       </c>
       <c r="O274" t="b">
         <v>1</v>
@@ -33705,19 +33762,19 @@
         <v>96</v>
       </c>
       <c r="J275" t="n">
-        <v>0.08</v>
+        <v>0.105</v>
       </c>
       <c r="K275" t="n">
-        <v>0.077</v>
+        <v>0.098</v>
       </c>
       <c r="L275" t="n">
-        <v>0.962</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="M275" t="n">
-        <v>0.67</v>
+        <v>0.613</v>
       </c>
       <c r="N275" t="n">
-        <v>1.297</v>
+        <v>1.334</v>
       </c>
       <c r="O275" t="b">
         <v>1</v>
@@ -33765,19 +33822,19 @@
         <v>96</v>
       </c>
       <c r="J276" t="n">
-        <v>0.101</v>
+        <v>0.102</v>
       </c>
       <c r="K276" t="n">
-        <v>0.089</v>
+        <v>0.122</v>
       </c>
       <c r="L276" t="n">
-        <v>0.887</v>
+        <v>1.199</v>
       </c>
       <c r="M276" t="n">
-        <v>0.618</v>
+        <v>0.822</v>
       </c>
       <c r="N276" t="n">
-        <v>1.178</v>
+        <v>1.77</v>
       </c>
       <c r="O276" t="b">
         <v>1</v>
@@ -33825,10 +33882,10 @@
         <v>96</v>
       </c>
       <c r="J277" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="K277" t="n">
         <v>-0.021</v>
-      </c>
-      <c r="K277" t="n">
-        <v>-0.043</v>
       </c>
       <c r="O277" t="b">
         <v>1</v>
@@ -33876,19 +33933,19 @@
         <v>96</v>
       </c>
       <c r="J278" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="K278" t="n">
         <v>0.103</v>
       </c>
-      <c r="K278" t="n">
-        <v>0.106</v>
-      </c>
       <c r="L278" t="n">
-        <v>1.024</v>
+        <v>0.96</v>
       </c>
       <c r="M278" t="n">
-        <v>0.793</v>
+        <v>0.667</v>
       </c>
       <c r="N278" t="n">
-        <v>1.326</v>
+        <v>1.389</v>
       </c>
       <c r="O278" t="b">
         <v>1</v>
@@ -34200,10 +34257,10 @@
         <v>4.427</v>
       </c>
       <c r="M284" t="n">
-        <v>2.56</v>
+        <v>2.576</v>
       </c>
       <c r="N284" t="n">
-        <v>6.058</v>
+        <v>5.94</v>
       </c>
       <c r="O284" t="b">
         <v>1</v>
@@ -34311,10 +34368,10 @@
         <v>5.392</v>
       </c>
       <c r="M286" t="n">
-        <v>2.782</v>
+        <v>2.775</v>
       </c>
       <c r="N286" t="n">
-        <v>6.817</v>
+        <v>6.837</v>
       </c>
       <c r="O286" t="b">
         <v>1</v>
@@ -34371,10 +34428,10 @@
         <v>1.753</v>
       </c>
       <c r="M287" t="n">
-        <v>1.458</v>
+        <v>1.459</v>
       </c>
       <c r="N287" t="n">
-        <v>2.112</v>
+        <v>2.12</v>
       </c>
       <c r="O287" t="b">
         <v>1</v>
@@ -34431,10 +34488,10 @@
         <v>2.617</v>
       </c>
       <c r="M288" t="n">
-        <v>1.939</v>
+        <v>1.957</v>
       </c>
       <c r="N288" t="n">
-        <v>3.998</v>
+        <v>3.973</v>
       </c>
       <c r="O288" t="b">
         <v>1</v>
@@ -34491,7 +34548,7 @@
         <v>1.151</v>
       </c>
       <c r="M289" t="n">
-        <v>1.04</v>
+        <v>1.039</v>
       </c>
       <c r="N289" t="n">
         <v>1.28</v>
@@ -38685,13 +38742,13 @@
         <v>1</v>
       </c>
       <c r="I360" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J360" t="n">
-        <v>-0.007</v>
+        <v>0</v>
       </c>
       <c r="K360" t="n">
-        <v>0.013</v>
+        <v>-0.014</v>
       </c>
       <c r="O360" t="b">
         <v>0</v>
@@ -38739,10 +38796,19 @@
         <v>96</v>
       </c>
       <c r="J361" t="n">
-        <v>0.016</v>
+        <v>0.06</v>
       </c>
       <c r="K361" t="n">
-        <v>0.027</v>
+        <v>0.023</v>
+      </c>
+      <c r="L361" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="M361" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="N361" t="n">
+        <v>0.8129999999999999</v>
       </c>
       <c r="O361" t="b">
         <v>1</v>
@@ -38787,22 +38853,22 @@
         <v>1</v>
       </c>
       <c r="I362" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J362" t="n">
-        <v>0.056</v>
+        <v>0.097</v>
       </c>
       <c r="K362" t="n">
-        <v>0.075</v>
+        <v>0.081</v>
       </c>
       <c r="L362" t="n">
-        <v>1.326</v>
+        <v>0.833</v>
       </c>
       <c r="M362" t="n">
-        <v>0.925</v>
+        <v>0.51</v>
       </c>
       <c r="N362" t="n">
-        <v>1.608</v>
+        <v>1.122</v>
       </c>
       <c r="O362" t="b">
         <v>1</v>
@@ -38850,19 +38916,19 @@
         <v>96</v>
       </c>
       <c r="J363" t="n">
-        <v>0.065</v>
+        <v>0.099</v>
       </c>
       <c r="K363" t="n">
-        <v>0.06</v>
+        <v>0.052</v>
       </c>
       <c r="L363" t="n">
-        <v>0.925</v>
+        <v>0.529</v>
       </c>
       <c r="M363" t="n">
-        <v>0.627</v>
+        <v>0.172</v>
       </c>
       <c r="N363" t="n">
-        <v>1.268</v>
+        <v>0.804</v>
       </c>
       <c r="O363" t="b">
         <v>1</v>
@@ -38910,10 +38976,19 @@
         <v>96</v>
       </c>
       <c r="J364" t="n">
-        <v>0.035</v>
+        <v>0.074</v>
       </c>
       <c r="K364" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
+      </c>
+      <c r="L364" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="M364" t="n">
+        <v>-0.08500000000000001</v>
+      </c>
+      <c r="N364" t="n">
+        <v>0.789</v>
       </c>
       <c r="O364" t="b">
         <v>1</v>
@@ -38961,10 +39036,10 @@
         <v>96</v>
       </c>
       <c r="J365" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="K365" t="n">
-        <v>0.028</v>
+        <v>0.038</v>
       </c>
       <c r="O365" t="b">
         <v>1</v>
@@ -39012,19 +39087,19 @@
         <v>96</v>
       </c>
       <c r="J366" t="n">
-        <v>0.063</v>
+        <v>0.074</v>
       </c>
       <c r="K366" t="n">
-        <v>0.058</v>
+        <v>0.052</v>
       </c>
       <c r="L366" t="n">
-        <v>0.908</v>
+        <v>0.705</v>
       </c>
       <c r="M366" t="n">
-        <v>0.576</v>
+        <v>0.272</v>
       </c>
       <c r="N366" t="n">
-        <v>1.249</v>
+        <v>1.117</v>
       </c>
       <c r="O366" t="b">
         <v>1</v>
@@ -39072,19 +39147,19 @@
         <v>96</v>
       </c>
       <c r="J367" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K367" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="L367" t="n">
-        <v>0.832</v>
+        <v>1.073</v>
       </c>
       <c r="M367" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="N367" t="n">
-        <v>1.116</v>
+        <v>1.601</v>
       </c>
       <c r="O367" t="b">
         <v>1</v>
@@ -39132,10 +39207,10 @@
         <v>96</v>
       </c>
       <c r="J368" t="n">
-        <v>-0.037</v>
+        <v>-0.035</v>
       </c>
       <c r="K368" t="n">
-        <v>-0.062</v>
+        <v>-0.066</v>
       </c>
       <c r="O368" t="b">
         <v>1</v>
@@ -39183,19 +39258,19 @@
         <v>96</v>
       </c>
       <c r="J369" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="K369" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.057</v>
       </c>
       <c r="L369" t="n">
-        <v>0.997</v>
+        <v>0.748</v>
       </c>
       <c r="M369" t="n">
-        <v>0.755</v>
+        <v>0.337</v>
       </c>
       <c r="N369" t="n">
-        <v>1.299</v>
+        <v>1.175</v>
       </c>
       <c r="O369" t="b">
         <v>1</v>
@@ -39456,10 +39531,10 @@
         <v>3.713</v>
       </c>
       <c r="M374" t="n">
-        <v>2.183</v>
+        <v>2.113</v>
       </c>
       <c r="N374" t="n">
-        <v>5.057</v>
+        <v>5.127</v>
       </c>
       <c r="O374" t="b">
         <v>1</v>
@@ -39567,10 +39642,10 @@
         <v>4.626</v>
       </c>
       <c r="M376" t="n">
-        <v>2.278</v>
+        <v>2.334</v>
       </c>
       <c r="N376" t="n">
-        <v>5.846</v>
+        <v>5.741</v>
       </c>
       <c r="O376" t="b">
         <v>1</v>
@@ -39627,10 +39702,10 @@
         <v>1.589</v>
       </c>
       <c r="M377" t="n">
-        <v>1.297</v>
+        <v>1.293</v>
       </c>
       <c r="N377" t="n">
-        <v>2</v>
+        <v>1.978</v>
       </c>
       <c r="O377" t="b">
         <v>1</v>
@@ -39687,10 +39762,10 @@
         <v>2.247</v>
       </c>
       <c r="M378" t="n">
-        <v>1.557</v>
+        <v>1.552</v>
       </c>
       <c r="N378" t="n">
-        <v>3.748</v>
+        <v>3.981</v>
       </c>
       <c r="O378" t="b">
         <v>1</v>
@@ -39750,7 +39825,7 @@
         <v>0.944</v>
       </c>
       <c r="N379" t="n">
-        <v>1.21</v>
+        <v>1.208</v>
       </c>
       <c r="O379" t="b">
         <v>1</v>
@@ -44325,13 +44400,13 @@
         <v>0</v>
       </c>
       <c r="I457" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J457" t="n">
-        <v>-0.011</v>
+        <v>-0.024</v>
       </c>
       <c r="K457" t="n">
-        <v>-0.017</v>
+        <v>-0.022</v>
       </c>
       <c r="O457" t="b">
         <v>1</v>
@@ -44376,13 +44451,13 @@
         <v>0</v>
       </c>
       <c r="I458" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J458" t="n">
-        <v>-0.005</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K458" t="n">
-        <v>-0.001</v>
+        <v>0.016</v>
       </c>
       <c r="O458" t="b">
         <v>1</v>
@@ -44427,13 +44502,22 @@
         <v>0</v>
       </c>
       <c r="I459" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J459" t="n">
-        <v>0.033</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="K459" t="n">
-        <v>0.037</v>
+        <v>0.061</v>
+      </c>
+      <c r="L459" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="M459" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="N459" t="n">
+        <v>1.253</v>
       </c>
       <c r="O459" t="b">
         <v>1</v>
@@ -44478,22 +44562,22 @@
         <v>0</v>
       </c>
       <c r="I460" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J460" t="n">
-        <v>0.098</v>
+        <v>0.104</v>
       </c>
       <c r="K460" t="n">
-        <v>0.099</v>
+        <v>0.114</v>
       </c>
       <c r="L460" t="n">
-        <v>1.014</v>
+        <v>1.09</v>
       </c>
       <c r="M460" t="n">
-        <v>0.743</v>
+        <v>0.826</v>
       </c>
       <c r="N460" t="n">
-        <v>1.325</v>
+        <v>1.485</v>
       </c>
       <c r="O460" t="b">
         <v>1</v>
@@ -44538,22 +44622,22 @@
         <v>0</v>
       </c>
       <c r="I461" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J461" t="n">
-        <v>0.132</v>
+        <v>0.123</v>
       </c>
       <c r="K461" t="n">
-        <v>0.128</v>
+        <v>0.136</v>
       </c>
       <c r="L461" t="n">
-        <v>0.964</v>
+        <v>1.109</v>
       </c>
       <c r="M461" t="n">
-        <v>0.776</v>
+        <v>0.895</v>
       </c>
       <c r="N461" t="n">
-        <v>1.171</v>
+        <v>1.498</v>
       </c>
       <c r="O461" t="b">
         <v>1</v>
@@ -44598,22 +44682,22 @@
         <v>0</v>
       </c>
       <c r="I462" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J462" t="n">
-        <v>0.097</v>
+        <v>0.117</v>
       </c>
       <c r="K462" t="n">
-        <v>0.099</v>
+        <v>0.116</v>
       </c>
       <c r="L462" t="n">
-        <v>1.025</v>
+        <v>0.992</v>
       </c>
       <c r="M462" t="n">
-        <v>0.757</v>
+        <v>0.789</v>
       </c>
       <c r="N462" t="n">
-        <v>1.394</v>
+        <v>1.307</v>
       </c>
       <c r="O462" t="b">
         <v>1</v>
@@ -44658,22 +44742,22 @@
         <v>0</v>
       </c>
       <c r="I463" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J463" t="n">
-        <v>0.144</v>
+        <v>0.176</v>
       </c>
       <c r="K463" t="n">
-        <v>0.154</v>
+        <v>0.176</v>
       </c>
       <c r="L463" t="n">
-        <v>1.074</v>
+        <v>0.998</v>
       </c>
       <c r="M463" t="n">
-        <v>0.885</v>
+        <v>0.833</v>
       </c>
       <c r="N463" t="n">
-        <v>1.296</v>
+        <v>1.226</v>
       </c>
       <c r="O463" t="b">
         <v>1</v>
@@ -44718,22 +44802,22 @@
         <v>0</v>
       </c>
       <c r="I464" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J464" t="n">
-        <v>0.14</v>
+        <v>0.171</v>
       </c>
       <c r="K464" t="n">
-        <v>0.145</v>
+        <v>0.179</v>
       </c>
       <c r="L464" t="n">
-        <v>1.037</v>
+        <v>1.046</v>
       </c>
       <c r="M464" t="n">
-        <v>0.833</v>
+        <v>0.851</v>
       </c>
       <c r="N464" t="n">
-        <v>1.276</v>
+        <v>1.294</v>
       </c>
       <c r="O464" t="b">
         <v>1</v>
@@ -44778,22 +44862,22 @@
         <v>0</v>
       </c>
       <c r="I465" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J465" t="n">
-        <v>0.146</v>
+        <v>0.184</v>
       </c>
       <c r="K465" t="n">
-        <v>0.176</v>
+        <v>0.197</v>
       </c>
       <c r="L465" t="n">
-        <v>1.211</v>
+        <v>1.067</v>
       </c>
       <c r="M465" t="n">
-        <v>1.039</v>
+        <v>0.909</v>
       </c>
       <c r="N465" t="n">
-        <v>1.454</v>
+        <v>1.262</v>
       </c>
       <c r="O465" t="b">
         <v>1</v>
@@ -44838,22 +44922,22 @@
         <v>0</v>
       </c>
       <c r="I466" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J466" t="n">
-        <v>0.218</v>
+        <v>0.234</v>
       </c>
       <c r="K466" t="n">
-        <v>0.231</v>
+        <v>0.236</v>
       </c>
       <c r="L466" t="n">
-        <v>1.063</v>
+        <v>1.005</v>
       </c>
       <c r="M466" t="n">
-        <v>0.927</v>
+        <v>0.892</v>
       </c>
       <c r="N466" t="n">
-        <v>1.217</v>
+        <v>1.139</v>
       </c>
       <c r="O466" t="b">
         <v>1</v>
@@ -44898,22 +44982,22 @@
         <v>0</v>
       </c>
       <c r="I467" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J467" t="n">
-        <v>0.204</v>
+        <v>0.232</v>
       </c>
       <c r="K467" t="n">
-        <v>0.202</v>
+        <v>0.239</v>
       </c>
       <c r="L467" t="n">
-        <v>0.992</v>
+        <v>1.03</v>
       </c>
       <c r="M467" t="n">
-        <v>0.849</v>
+        <v>0.889</v>
       </c>
       <c r="N467" t="n">
-        <v>1.134</v>
+        <v>1.202</v>
       </c>
       <c r="O467" t="b">
         <v>1</v>
@@ -45024,7 +45108,7 @@
         <v>-1.133</v>
       </c>
       <c r="N469" t="n">
-        <v>1.209</v>
+        <v>1.28</v>
       </c>
       <c r="O469" t="b">
         <v>0</v>
@@ -45081,10 +45165,10 @@
         <v>-0.003</v>
       </c>
       <c r="M470" t="n">
-        <v>-1.025</v>
+        <v>-1.109</v>
       </c>
       <c r="N470" t="n">
-        <v>1.392</v>
+        <v>1.32</v>
       </c>
       <c r="O470" t="b">
         <v>0</v>
@@ -45141,10 +45225,10 @@
         <v>1.134</v>
       </c>
       <c r="M471" t="n">
-        <v>0.53</v>
+        <v>0.509</v>
       </c>
       <c r="N471" t="n">
-        <v>1.84</v>
+        <v>1.872</v>
       </c>
       <c r="O471" t="b">
         <v>1</v>
@@ -45201,10 +45285,10 @@
         <v>1.504</v>
       </c>
       <c r="M472" t="n">
-        <v>0.928</v>
+        <v>0.908</v>
       </c>
       <c r="N472" t="n">
-        <v>2.403</v>
+        <v>2.447</v>
       </c>
       <c r="O472" t="b">
         <v>1</v>
@@ -45261,10 +45345,10 @@
         <v>1.698</v>
       </c>
       <c r="M473" t="n">
-        <v>1.208</v>
+        <v>1.19</v>
       </c>
       <c r="N473" t="n">
-        <v>2.528</v>
+        <v>2.532</v>
       </c>
       <c r="O473" t="b">
         <v>1</v>
@@ -45321,10 +45405,10 @@
         <v>1.974</v>
       </c>
       <c r="M474" t="n">
-        <v>1.267</v>
+        <v>1.27</v>
       </c>
       <c r="N474" t="n">
-        <v>3.105</v>
+        <v>3.115</v>
       </c>
       <c r="O474" t="b">
         <v>1</v>
@@ -45381,10 +45465,10 @@
         <v>2.975</v>
       </c>
       <c r="M475" t="n">
-        <v>1.794</v>
+        <v>1.729</v>
       </c>
       <c r="N475" t="n">
-        <v>4.289</v>
+        <v>4.274</v>
       </c>
       <c r="O475" t="b">
         <v>1</v>
@@ -50106,10 +50190,10 @@
         <v>96</v>
       </c>
       <c r="J556" t="n">
-        <v>-0.016</v>
+        <v>-0.031</v>
       </c>
       <c r="K556" t="n">
-        <v>-0.019</v>
+        <v>-0.046</v>
       </c>
       <c r="O556" t="b">
         <v>1</v>
@@ -50154,13 +50238,13 @@
         <v>0</v>
       </c>
       <c r="I557" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J557" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="K557" t="n">
         <v>-0.01</v>
-      </c>
-      <c r="K557" t="n">
-        <v>-0.004</v>
       </c>
       <c r="O557" t="b">
         <v>1</v>
@@ -50208,11 +50292,20 @@
         <v>96</v>
       </c>
       <c r="J558" t="n">
-        <v>0.028</v>
+        <v>0.062</v>
       </c>
       <c r="K558" t="n">
         <v>0.035</v>
       </c>
+      <c r="L558" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="M558" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="N558" t="n">
+        <v>0.988</v>
+      </c>
       <c r="O558" t="b">
         <v>1</v>
       </c>
@@ -50259,19 +50352,19 @@
         <v>96</v>
       </c>
       <c r="J559" t="n">
-        <v>0.092</v>
+        <v>0.095</v>
       </c>
       <c r="K559" t="n">
-        <v>0.097</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L559" t="n">
-        <v>1.049</v>
+        <v>0.917</v>
       </c>
       <c r="M559" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.634</v>
       </c>
       <c r="N559" t="n">
-        <v>1.388</v>
+        <v>1.19</v>
       </c>
       <c r="O559" t="b">
         <v>1</v>
@@ -50319,19 +50412,19 @@
         <v>96</v>
       </c>
       <c r="J560" t="n">
-        <v>0.127</v>
+        <v>0.118</v>
       </c>
       <c r="K560" t="n">
-        <v>0.125</v>
+        <v>0.115</v>
       </c>
       <c r="L560" t="n">
-        <v>0.987</v>
+        <v>0.969</v>
       </c>
       <c r="M560" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.741</v>
       </c>
       <c r="N560" t="n">
-        <v>1.22</v>
+        <v>1.261</v>
       </c>
       <c r="O560" t="b">
         <v>1</v>
@@ -50379,19 +50472,19 @@
         <v>96</v>
       </c>
       <c r="J561" t="n">
-        <v>0.091</v>
+        <v>0.109</v>
       </c>
       <c r="K561" t="n">
-        <v>0.097</v>
+        <v>0.092</v>
       </c>
       <c r="L561" t="n">
-        <v>1.061</v>
+        <v>0.849</v>
       </c>
       <c r="M561" t="n">
-        <v>0.819</v>
+        <v>0.6</v>
       </c>
       <c r="N561" t="n">
-        <v>1.391</v>
+        <v>1.038</v>
       </c>
       <c r="O561" t="b">
         <v>1</v>
@@ -50439,19 +50532,19 @@
         <v>96</v>
       </c>
       <c r="J562" t="n">
-        <v>0.138</v>
+        <v>0.164</v>
       </c>
       <c r="K562" t="n">
-        <v>0.152</v>
+        <v>0.148</v>
       </c>
       <c r="L562" t="n">
-        <v>1.1</v>
+        <v>0.904</v>
       </c>
       <c r="M562" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.726</v>
       </c>
       <c r="N562" t="n">
-        <v>1.353</v>
+        <v>1.088</v>
       </c>
       <c r="O562" t="b">
         <v>1</v>
@@ -50499,19 +50592,19 @@
         <v>96</v>
       </c>
       <c r="J563" t="n">
-        <v>0.134</v>
+        <v>0.159</v>
       </c>
       <c r="K563" t="n">
-        <v>0.142</v>
+        <v>0.153</v>
       </c>
       <c r="L563" t="n">
-        <v>1.062</v>
+        <v>0.96</v>
       </c>
       <c r="M563" t="n">
-        <v>0.871</v>
+        <v>0.763</v>
       </c>
       <c r="N563" t="n">
-        <v>1.331</v>
+        <v>1.191</v>
       </c>
       <c r="O563" t="b">
         <v>1</v>
@@ -50559,19 +50652,19 @@
         <v>96</v>
       </c>
       <c r="J564" t="n">
-        <v>0.14</v>
+        <v>0.172</v>
       </c>
       <c r="K564" t="n">
-        <v>0.174</v>
+        <v>0.176</v>
       </c>
       <c r="L564" t="n">
-        <v>1.242</v>
+        <v>1.023</v>
       </c>
       <c r="M564" t="n">
-        <v>1.075</v>
+        <v>0.862</v>
       </c>
       <c r="N564" t="n">
-        <v>1.492</v>
+        <v>1.187</v>
       </c>
       <c r="O564" t="b">
         <v>1</v>
@@ -50619,19 +50712,19 @@
         <v>96</v>
       </c>
       <c r="J565" t="n">
-        <v>0.212</v>
+        <v>0.23</v>
       </c>
       <c r="K565" t="n">
-        <v>0.229</v>
+        <v>0.217</v>
       </c>
       <c r="L565" t="n">
-        <v>1.079</v>
+        <v>0.944</v>
       </c>
       <c r="M565" t="n">
-        <v>0.967</v>
+        <v>0.84</v>
       </c>
       <c r="N565" t="n">
-        <v>1.206</v>
+        <v>1.047</v>
       </c>
       <c r="O565" t="b">
         <v>1</v>
@@ -50679,19 +50772,19 @@
         <v>96</v>
       </c>
       <c r="J566" t="n">
-        <v>0.198</v>
+        <v>0.226</v>
       </c>
       <c r="K566" t="n">
-        <v>0.199</v>
+        <v>0.214</v>
       </c>
       <c r="L566" t="n">
-        <v>1.008</v>
+        <v>0.949</v>
       </c>
       <c r="M566" t="n">
-        <v>0.877</v>
+        <v>0.803</v>
       </c>
       <c r="N566" t="n">
-        <v>1.15</v>
+        <v>1.098</v>
       </c>
       <c r="O566" t="b">
         <v>1</v>
@@ -50901,10 +50994,10 @@
         <v>1.392</v>
       </c>
       <c r="M570" t="n">
-        <v>0.661</v>
+        <v>0.675</v>
       </c>
       <c r="N570" t="n">
-        <v>2.466</v>
+        <v>2.45</v>
       </c>
       <c r="O570" t="b">
         <v>1</v>
@@ -50961,10 +51054,10 @@
         <v>1.903</v>
       </c>
       <c r="M571" t="n">
-        <v>1.135</v>
+        <v>1.099</v>
       </c>
       <c r="N571" t="n">
-        <v>3.281</v>
+        <v>3.18</v>
       </c>
       <c r="O571" t="b">
         <v>1</v>
@@ -51021,10 +51114,10 @@
         <v>2.039</v>
       </c>
       <c r="M572" t="n">
-        <v>1.349</v>
+        <v>1.391</v>
       </c>
       <c r="N572" t="n">
-        <v>3.45</v>
+        <v>3.454</v>
       </c>
       <c r="O572" t="b">
         <v>1</v>
@@ -51081,10 +51174,10 @@
         <v>2.736</v>
       </c>
       <c r="M573" t="n">
-        <v>1.499</v>
+        <v>1.527</v>
       </c>
       <c r="N573" t="n">
-        <v>3.993</v>
+        <v>4.018</v>
       </c>
       <c r="O573" t="b">
         <v>1</v>
@@ -55506,13 +55599,13 @@
         <v>1</v>
       </c>
       <c r="I648" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J648" t="n">
-        <v>0.006</v>
+        <v>0.03</v>
       </c>
       <c r="K648" t="n">
-        <v>0.015</v>
+        <v>0.039</v>
       </c>
       <c r="O648" t="b">
         <v>1</v>
@@ -55560,10 +55653,19 @@
         <v>96</v>
       </c>
       <c r="J649" t="n">
-        <v>0.044</v>
+        <v>0.093</v>
       </c>
       <c r="K649" t="n">
-        <v>0.054</v>
+        <v>0.081</v>
+      </c>
+      <c r="L649" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="M649" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="N649" t="n">
+        <v>1.279</v>
       </c>
       <c r="O649" t="b">
         <v>1</v>
@@ -55611,19 +55713,19 @@
         <v>96</v>
       </c>
       <c r="J650" t="n">
-        <v>0.109</v>
+        <v>0.126</v>
       </c>
       <c r="K650" t="n">
-        <v>0.116</v>
+        <v>0.133</v>
       </c>
       <c r="L650" t="n">
-        <v>1.067</v>
+        <v>1.056</v>
       </c>
       <c r="M650" t="n">
-        <v>0.829</v>
+        <v>0.864</v>
       </c>
       <c r="N650" t="n">
-        <v>1.356</v>
+        <v>1.334</v>
       </c>
       <c r="O650" t="b">
         <v>1</v>
@@ -55671,19 +55773,19 @@
         <v>96</v>
       </c>
       <c r="J651" t="n">
-        <v>0.143</v>
+        <v>0.149</v>
       </c>
       <c r="K651" t="n">
-        <v>0.144</v>
+        <v>0.16</v>
       </c>
       <c r="L651" t="n">
-        <v>1.008</v>
+        <v>1.076</v>
       </c>
       <c r="M651" t="n">
-        <v>0.832</v>
+        <v>0.883</v>
       </c>
       <c r="N651" t="n">
-        <v>1.217</v>
+        <v>1.352</v>
       </c>
       <c r="O651" t="b">
         <v>1</v>
@@ -55731,19 +55833,19 @@
         <v>96</v>
       </c>
       <c r="J652" t="n">
-        <v>0.107</v>
+        <v>0.139</v>
       </c>
       <c r="K652" t="n">
-        <v>0.116</v>
+        <v>0.138</v>
       </c>
       <c r="L652" t="n">
-        <v>1.077</v>
+        <v>0.99</v>
       </c>
       <c r="M652" t="n">
-        <v>0.852</v>
+        <v>0.796</v>
       </c>
       <c r="N652" t="n">
-        <v>1.4</v>
+        <v>1.199</v>
       </c>
       <c r="O652" t="b">
         <v>1</v>
@@ -55791,19 +55893,19 @@
         <v>96</v>
       </c>
       <c r="J653" t="n">
-        <v>0.154</v>
+        <v>0.195</v>
       </c>
       <c r="K653" t="n">
-        <v>0.171</v>
+        <v>0.194</v>
       </c>
       <c r="L653" t="n">
-        <v>1.107</v>
+        <v>0.996</v>
       </c>
       <c r="M653" t="n">
-        <v>0.918</v>
+        <v>0.861</v>
       </c>
       <c r="N653" t="n">
-        <v>1.326</v>
+        <v>1.165</v>
       </c>
       <c r="O653" t="b">
         <v>1</v>
@@ -55851,19 +55953,19 @@
         <v>96</v>
       </c>
       <c r="J654" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="K654" t="n">
-        <v>0.161</v>
+        <v>0.199</v>
       </c>
       <c r="L654" t="n">
-        <v>1.074</v>
+        <v>1.046</v>
       </c>
       <c r="M654" t="n">
-        <v>0.886</v>
+        <v>0.862</v>
       </c>
       <c r="N654" t="n">
-        <v>1.302</v>
+        <v>1.292</v>
       </c>
       <c r="O654" t="b">
         <v>1</v>
@@ -55911,19 +56013,19 @@
         <v>96</v>
       </c>
       <c r="J655" t="n">
-        <v>0.156</v>
+        <v>0.203</v>
       </c>
       <c r="K655" t="n">
-        <v>0.193</v>
+        <v>0.221</v>
       </c>
       <c r="L655" t="n">
-        <v>1.234</v>
+        <v>1.093</v>
       </c>
       <c r="M655" t="n">
-        <v>1.075</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="N655" t="n">
-        <v>1.437</v>
+        <v>1.274</v>
       </c>
       <c r="O655" t="b">
         <v>1</v>
@@ -55971,19 +56073,19 @@
         <v>96</v>
       </c>
       <c r="J656" t="n">
-        <v>0.228</v>
+        <v>0.261</v>
       </c>
       <c r="K656" t="n">
-        <v>0.248</v>
+        <v>0.263</v>
       </c>
       <c r="L656" t="n">
-        <v>1.086</v>
+        <v>1.008</v>
       </c>
       <c r="M656" t="n">
-        <v>0.967</v>
+        <v>0.894</v>
       </c>
       <c r="N656" t="n">
-        <v>1.208</v>
+        <v>1.134</v>
       </c>
       <c r="O656" t="b">
         <v>1</v>
@@ -56031,19 +56133,19 @@
         <v>96</v>
       </c>
       <c r="J657" t="n">
-        <v>0.214</v>
+        <v>0.257</v>
       </c>
       <c r="K657" t="n">
-        <v>0.219</v>
+        <v>0.26</v>
       </c>
       <c r="L657" t="n">
-        <v>1.02</v>
+        <v>1.013</v>
       </c>
       <c r="M657" t="n">
-        <v>0.896</v>
+        <v>0.9</v>
       </c>
       <c r="N657" t="n">
-        <v>1.151</v>
+        <v>1.149</v>
       </c>
       <c r="O657" t="b">
         <v>1</v>
@@ -56202,10 +56304,10 @@
         <v>1.939</v>
       </c>
       <c r="M660" t="n">
-        <v>1.267</v>
+        <v>1.296</v>
       </c>
       <c r="N660" t="n">
-        <v>3.061</v>
+        <v>2.947</v>
       </c>
       <c r="O660" t="b">
         <v>1</v>
@@ -56262,10 +56364,10 @@
         <v>2.454</v>
       </c>
       <c r="M661" t="n">
-        <v>1.56</v>
+        <v>1.548</v>
       </c>
       <c r="N661" t="n">
-        <v>3.978</v>
+        <v>3.977</v>
       </c>
       <c r="O661" t="b">
         <v>1</v>
@@ -56322,10 +56424,10 @@
         <v>2.44</v>
       </c>
       <c r="M662" t="n">
-        <v>1.748</v>
+        <v>1.738</v>
       </c>
       <c r="N662" t="n">
-        <v>3.813</v>
+        <v>3.946</v>
       </c>
       <c r="O662" t="b">
         <v>1</v>
@@ -56382,10 +56484,10 @@
         <v>3.441</v>
       </c>
       <c r="M663" t="n">
-        <v>2.018</v>
+        <v>2.072</v>
       </c>
       <c r="N663" t="n">
-        <v>4.969</v>
+        <v>5.007</v>
       </c>
       <c r="O663" t="b">
         <v>1</v>
@@ -60807,13 +60909,13 @@
         <v>1</v>
       </c>
       <c r="I738" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J738" t="n">
-        <v>0.006</v>
+        <v>0.03</v>
       </c>
       <c r="K738" t="n">
-        <v>0.015</v>
+        <v>0.039</v>
       </c>
       <c r="O738" t="b">
         <v>1</v>
@@ -60861,10 +60963,19 @@
         <v>96</v>
       </c>
       <c r="J739" t="n">
-        <v>0.044</v>
+        <v>0.093</v>
       </c>
       <c r="K739" t="n">
-        <v>0.054</v>
+        <v>0.081</v>
+      </c>
+      <c r="L739" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="M739" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="N739" t="n">
+        <v>1.279</v>
       </c>
       <c r="O739" t="b">
         <v>1</v>
@@ -60912,19 +61023,19 @@
         <v>96</v>
       </c>
       <c r="J740" t="n">
-        <v>0.109</v>
+        <v>0.126</v>
       </c>
       <c r="K740" t="n">
-        <v>0.116</v>
+        <v>0.133</v>
       </c>
       <c r="L740" t="n">
-        <v>1.067</v>
+        <v>1.056</v>
       </c>
       <c r="M740" t="n">
-        <v>0.829</v>
+        <v>0.864</v>
       </c>
       <c r="N740" t="n">
-        <v>1.356</v>
+        <v>1.334</v>
       </c>
       <c r="O740" t="b">
         <v>1</v>
@@ -60972,19 +61083,19 @@
         <v>96</v>
       </c>
       <c r="J741" t="n">
-        <v>0.143</v>
+        <v>0.149</v>
       </c>
       <c r="K741" t="n">
-        <v>0.144</v>
+        <v>0.16</v>
       </c>
       <c r="L741" t="n">
-        <v>1.008</v>
+        <v>1.076</v>
       </c>
       <c r="M741" t="n">
-        <v>0.832</v>
+        <v>0.883</v>
       </c>
       <c r="N741" t="n">
-        <v>1.217</v>
+        <v>1.352</v>
       </c>
       <c r="O741" t="b">
         <v>1</v>
@@ -61032,19 +61143,19 @@
         <v>96</v>
       </c>
       <c r="J742" t="n">
-        <v>0.107</v>
+        <v>0.139</v>
       </c>
       <c r="K742" t="n">
-        <v>0.116</v>
+        <v>0.138</v>
       </c>
       <c r="L742" t="n">
-        <v>1.077</v>
+        <v>0.99</v>
       </c>
       <c r="M742" t="n">
-        <v>0.852</v>
+        <v>0.796</v>
       </c>
       <c r="N742" t="n">
-        <v>1.4</v>
+        <v>1.199</v>
       </c>
       <c r="O742" t="b">
         <v>1</v>
@@ -61092,19 +61203,19 @@
         <v>96</v>
       </c>
       <c r="J743" t="n">
-        <v>0.154</v>
+        <v>0.195</v>
       </c>
       <c r="K743" t="n">
-        <v>0.171</v>
+        <v>0.194</v>
       </c>
       <c r="L743" t="n">
-        <v>1.107</v>
+        <v>0.996</v>
       </c>
       <c r="M743" t="n">
-        <v>0.918</v>
+        <v>0.861</v>
       </c>
       <c r="N743" t="n">
-        <v>1.326</v>
+        <v>1.165</v>
       </c>
       <c r="O743" t="b">
         <v>1</v>
@@ -61152,19 +61263,19 @@
         <v>96</v>
       </c>
       <c r="J744" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="K744" t="n">
-        <v>0.161</v>
+        <v>0.199</v>
       </c>
       <c r="L744" t="n">
-        <v>1.074</v>
+        <v>1.046</v>
       </c>
       <c r="M744" t="n">
-        <v>0.886</v>
+        <v>0.862</v>
       </c>
       <c r="N744" t="n">
-        <v>1.302</v>
+        <v>1.292</v>
       </c>
       <c r="O744" t="b">
         <v>1</v>
@@ -61212,19 +61323,19 @@
         <v>96</v>
       </c>
       <c r="J745" t="n">
-        <v>0.156</v>
+        <v>0.203</v>
       </c>
       <c r="K745" t="n">
-        <v>0.193</v>
+        <v>0.221</v>
       </c>
       <c r="L745" t="n">
-        <v>1.234</v>
+        <v>1.093</v>
       </c>
       <c r="M745" t="n">
-        <v>1.075</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="N745" t="n">
-        <v>1.437</v>
+        <v>1.274</v>
       </c>
       <c r="O745" t="b">
         <v>1</v>
@@ -61272,19 +61383,19 @@
         <v>96</v>
       </c>
       <c r="J746" t="n">
-        <v>0.228</v>
+        <v>0.261</v>
       </c>
       <c r="K746" t="n">
-        <v>0.248</v>
+        <v>0.263</v>
       </c>
       <c r="L746" t="n">
-        <v>1.086</v>
+        <v>1.008</v>
       </c>
       <c r="M746" t="n">
-        <v>0.967</v>
+        <v>0.894</v>
       </c>
       <c r="N746" t="n">
-        <v>1.208</v>
+        <v>1.134</v>
       </c>
       <c r="O746" t="b">
         <v>1</v>
@@ -61332,19 +61443,19 @@
         <v>96</v>
       </c>
       <c r="J747" t="n">
-        <v>0.214</v>
+        <v>0.257</v>
       </c>
       <c r="K747" t="n">
-        <v>0.219</v>
+        <v>0.26</v>
       </c>
       <c r="L747" t="n">
-        <v>1.02</v>
+        <v>1.013</v>
       </c>
       <c r="M747" t="n">
-        <v>0.896</v>
+        <v>0.9</v>
       </c>
       <c r="N747" t="n">
-        <v>1.151</v>
+        <v>1.149</v>
       </c>
       <c r="O747" t="b">
         <v>1</v>
@@ -61503,10 +61614,10 @@
         <v>1.939</v>
       </c>
       <c r="M750" t="n">
-        <v>1.267</v>
+        <v>1.296</v>
       </c>
       <c r="N750" t="n">
-        <v>3.061</v>
+        <v>2.947</v>
       </c>
       <c r="O750" t="b">
         <v>1</v>
@@ -61563,10 +61674,10 @@
         <v>2.454</v>
       </c>
       <c r="M751" t="n">
-        <v>1.56</v>
+        <v>1.548</v>
       </c>
       <c r="N751" t="n">
-        <v>3.978</v>
+        <v>3.977</v>
       </c>
       <c r="O751" t="b">
         <v>1</v>
@@ -61623,10 +61734,10 @@
         <v>2.44</v>
       </c>
       <c r="M752" t="n">
-        <v>1.748</v>
+        <v>1.738</v>
       </c>
       <c r="N752" t="n">
-        <v>3.813</v>
+        <v>3.946</v>
       </c>
       <c r="O752" t="b">
         <v>1</v>
@@ -61683,10 +61794,10 @@
         <v>3.441</v>
       </c>
       <c r="M753" t="n">
-        <v>2.018</v>
+        <v>2.072</v>
       </c>
       <c r="N753" t="n">
-        <v>4.969</v>
+        <v>5.007</v>
       </c>
       <c r="O753" t="b">
         <v>1</v>
@@ -66099,16 +66210,16 @@
         <v>1</v>
       </c>
       <c r="I828" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J828" t="n">
-        <v>-0.029</v>
+        <v>0.005</v>
       </c>
       <c r="K828" t="n">
-        <v>-0.007</v>
+        <v>-0.008</v>
       </c>
       <c r="O828" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P828" t="n">
         <v>0.05</v>
@@ -66150,13 +66261,13 @@
         <v>1</v>
       </c>
       <c r="I829" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J829" t="n">
-        <v>0.002</v>
+        <v>0.03</v>
       </c>
       <c r="K829" t="n">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
       <c r="O829" t="b">
         <v>1</v>
@@ -66201,13 +66312,22 @@
         <v>1</v>
       </c>
       <c r="I830" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="J830" t="n">
-        <v>0.045</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="K830" t="n">
-        <v>0.052</v>
+        <v>0.059</v>
+      </c>
+      <c r="L830" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M830" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="N830" t="n">
+        <v>1.213</v>
       </c>
       <c r="O830" t="b">
         <v>1</v>
@@ -66252,13 +66372,22 @@
         <v>1</v>
       </c>
       <c r="I831" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J831" t="n">
-        <v>0.049</v>
+        <v>0.074</v>
       </c>
       <c r="K831" t="n">
-        <v>0.056</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L831" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="M831" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="N831" t="n">
+        <v>1.475</v>
       </c>
       <c r="O831" t="b">
         <v>1</v>
@@ -66303,22 +66432,22 @@
         <v>1</v>
       </c>
       <c r="I832" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J832" t="n">
-        <v>0.066</v>
+        <v>0.091</v>
       </c>
       <c r="K832" t="n">
-        <v>0.063</v>
+        <v>0.08</v>
       </c>
       <c r="L832" t="n">
-        <v>0.96</v>
+        <v>0.876</v>
       </c>
       <c r="M832" t="n">
-        <v>0.635</v>
+        <v>0.489</v>
       </c>
       <c r="N832" t="n">
-        <v>1.306</v>
+        <v>1.287</v>
       </c>
       <c r="O832" t="b">
         <v>1</v>
@@ -66363,22 +66492,22 @@
         <v>1</v>
       </c>
       <c r="I833" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J833" t="n">
-        <v>0.08</v>
+        <v>0.098</v>
       </c>
       <c r="K833" t="n">
-        <v>0.093</v>
+        <v>0.105</v>
       </c>
       <c r="L833" t="n">
-        <v>1.153</v>
+        <v>1.076</v>
       </c>
       <c r="M833" t="n">
-        <v>0.887</v>
+        <v>0.741</v>
       </c>
       <c r="N833" t="n">
-        <v>1.512</v>
+        <v>1.542</v>
       </c>
       <c r="O833" t="b">
         <v>1</v>
@@ -66423,22 +66552,22 @@
         <v>1</v>
       </c>
       <c r="I834" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J834" t="n">
-        <v>0.056</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K834" t="n">
-        <v>0.062</v>
+        <v>0.073</v>
       </c>
       <c r="L834" t="n">
-        <v>1.104</v>
+        <v>1.064</v>
       </c>
       <c r="M834" t="n">
-        <v>0.744</v>
+        <v>0.59</v>
       </c>
       <c r="N834" t="n">
-        <v>1.446</v>
+        <v>1.563</v>
       </c>
       <c r="O834" t="b">
         <v>1</v>
@@ -66483,22 +66612,22 @@
         <v>1</v>
       </c>
       <c r="I835" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J835" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.105</v>
       </c>
       <c r="K835" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="L835" t="n">
-        <v>1.017</v>
+        <v>0.795</v>
       </c>
       <c r="M835" t="n">
-        <v>0.746</v>
+        <v>0.486</v>
       </c>
       <c r="N835" t="n">
-        <v>1.36</v>
+        <v>1.155</v>
       </c>
       <c r="O835" t="b">
         <v>1</v>
@@ -66543,22 +66672,22 @@
         <v>1</v>
       </c>
       <c r="I836" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J836" t="n">
-        <v>0.123</v>
+        <v>0.131</v>
       </c>
       <c r="K836" t="n">
-        <v>0.118</v>
+        <v>0.122</v>
       </c>
       <c r="L836" t="n">
-        <v>0.96</v>
+        <v>0.931</v>
       </c>
       <c r="M836" t="n">
-        <v>0.757</v>
+        <v>0.652</v>
       </c>
       <c r="N836" t="n">
-        <v>1.265</v>
+        <v>1.232</v>
       </c>
       <c r="O836" t="b">
         <v>1</v>
@@ -66603,22 +66732,22 @@
         <v>1</v>
       </c>
       <c r="I837" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J837" t="n">
-        <v>0.141</v>
+        <v>0.117</v>
       </c>
       <c r="K837" t="n">
-        <v>0.113</v>
+        <v>0.111</v>
       </c>
       <c r="L837" t="n">
-        <v>0.802</v>
+        <v>0.945</v>
       </c>
       <c r="M837" t="n">
-        <v>0.642</v>
+        <v>0.638</v>
       </c>
       <c r="N837" t="n">
-        <v>0.978</v>
+        <v>1.286</v>
       </c>
       <c r="O837" t="b">
         <v>1</v>
@@ -66879,10 +67008,10 @@
         <v>1.832</v>
       </c>
       <c r="M842" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="N842" t="n">
-        <v>2.956</v>
+        <v>2.905</v>
       </c>
       <c r="O842" t="b">
         <v>1</v>
@@ -66939,10 +67068,10 @@
         <v>2.072</v>
       </c>
       <c r="M843" t="n">
-        <v>1.278</v>
+        <v>1.301</v>
       </c>
       <c r="N843" t="n">
-        <v>3.522</v>
+        <v>3.452</v>
       </c>
       <c r="O843" t="b">
         <v>1</v>
@@ -66999,10 +67128,10 @@
         <v>1.988</v>
       </c>
       <c r="M844" t="n">
-        <v>1.379</v>
+        <v>1.373</v>
       </c>
       <c r="N844" t="n">
-        <v>3.272</v>
+        <v>3.26</v>
       </c>
       <c r="O844" t="b">
         <v>1</v>
@@ -67059,10 +67188,10 @@
         <v>2.263</v>
       </c>
       <c r="M845" t="n">
-        <v>1.581</v>
+        <v>1.582</v>
       </c>
       <c r="N845" t="n">
-        <v>3.706</v>
+        <v>3.802</v>
       </c>
       <c r="O845" t="b">
         <v>1</v>
@@ -67119,10 +67248,10 @@
         <v>1.483</v>
       </c>
       <c r="M846" t="n">
-        <v>1.197</v>
+        <v>1.191</v>
       </c>
       <c r="N846" t="n">
-        <v>1.881</v>
+        <v>1.862</v>
       </c>
       <c r="O846" t="b">
         <v>1</v>
@@ -67179,10 +67308,10 @@
         <v>1.657</v>
       </c>
       <c r="M847" t="n">
-        <v>1.303</v>
+        <v>1.305</v>
       </c>
       <c r="N847" t="n">
-        <v>2.151</v>
+        <v>2.168</v>
       </c>
       <c r="O847" t="b">
         <v>1</v>
@@ -71757,13 +71886,13 @@
         <v>0</v>
       </c>
       <c r="I925" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J925" t="n">
-        <v>0.007</v>
+        <v>-0.003</v>
       </c>
       <c r="K925" t="n">
-        <v>-0.003</v>
+        <v>0.002</v>
       </c>
       <c r="O925" t="b">
         <v>0</v>
@@ -71808,16 +71937,16 @@
         <v>0</v>
       </c>
       <c r="I926" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J926" t="n">
-        <v>-0.022</v>
+        <v>0.002</v>
       </c>
       <c r="K926" t="n">
-        <v>-0.01</v>
+        <v>-0.006</v>
       </c>
       <c r="O926" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P926" t="n">
         <v>0.05</v>
@@ -71859,13 +71988,13 @@
         <v>0</v>
       </c>
       <c r="I927" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J927" t="n">
-        <v>0.01</v>
+        <v>0.035</v>
       </c>
       <c r="K927" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="O927" t="b">
         <v>1</v>
@@ -71910,22 +72039,22 @@
         <v>0</v>
       </c>
       <c r="I928" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="J928" t="n">
-        <v>0.052</v>
+        <v>0.064</v>
       </c>
       <c r="K928" t="n">
-        <v>0.049</v>
+        <v>0.06</v>
       </c>
       <c r="L928" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="M928" t="n">
-        <v>0.522</v>
+        <v>0.458</v>
       </c>
       <c r="N928" t="n">
-        <v>1.276</v>
+        <v>1.381</v>
       </c>
       <c r="O928" t="b">
         <v>1</v>
@@ -71970,22 +72099,22 @@
         <v>0</v>
       </c>
       <c r="I929" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J929" t="n">
-        <v>0.056</v>
+        <v>0.077</v>
       </c>
       <c r="K929" t="n">
-        <v>0.053</v>
+        <v>0.078</v>
       </c>
       <c r="L929" t="n">
-        <v>0.946</v>
+        <v>1.013</v>
       </c>
       <c r="M929" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.653</v>
       </c>
       <c r="N929" t="n">
-        <v>1.299</v>
+        <v>1.474</v>
       </c>
       <c r="O929" t="b">
         <v>1</v>
@@ -72030,22 +72159,22 @@
         <v>0</v>
       </c>
       <c r="I930" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J930" t="n">
-        <v>0.073</v>
+        <v>0.079</v>
       </c>
       <c r="K930" t="n">
-        <v>0.06</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="L930" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.899</v>
       </c>
       <c r="M930" t="n">
-        <v>0.426</v>
+        <v>0.538</v>
       </c>
       <c r="N930" t="n">
-        <v>1.195</v>
+        <v>1.329</v>
       </c>
       <c r="O930" t="b">
         <v>1</v>
@@ -72090,22 +72219,22 @@
         <v>0</v>
       </c>
       <c r="I931" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J931" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.089</v>
       </c>
       <c r="K931" t="n">
-        <v>0.089</v>
+        <v>0.1</v>
       </c>
       <c r="L931" t="n">
-        <v>1.018</v>
+        <v>1.132</v>
       </c>
       <c r="M931" t="n">
-        <v>0.743</v>
+        <v>0.857</v>
       </c>
       <c r="N931" t="n">
-        <v>1.402</v>
+        <v>1.551</v>
       </c>
       <c r="O931" t="b">
         <v>1</v>
@@ -72150,22 +72279,22 @@
         <v>0</v>
       </c>
       <c r="I932" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J932" t="n">
-        <v>0.064</v>
+        <v>0.065</v>
       </c>
       <c r="K932" t="n">
-        <v>0.059</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L932" t="n">
-        <v>0.925</v>
+        <v>1.073</v>
       </c>
       <c r="M932" t="n">
-        <v>0.548</v>
+        <v>0.649</v>
       </c>
       <c r="N932" t="n">
-        <v>1.299</v>
+        <v>1.617</v>
       </c>
       <c r="O932" t="b">
         <v>1</v>
@@ -72210,22 +72339,22 @@
         <v>0</v>
       </c>
       <c r="I933" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J933" t="n">
-        <v>0.091</v>
+        <v>0.108</v>
       </c>
       <c r="K933" t="n">
-        <v>0.082</v>
+        <v>0.09</v>
       </c>
       <c r="L933" t="n">
-        <v>0.899</v>
+        <v>0.829</v>
       </c>
       <c r="M933" t="n">
-        <v>0.593</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="N933" t="n">
-        <v>1.223</v>
+        <v>1.161</v>
       </c>
       <c r="O933" t="b">
         <v>1</v>
@@ -72270,22 +72399,22 @@
         <v>0</v>
       </c>
       <c r="I934" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="J934" t="n">
         <v>0.13</v>
       </c>
       <c r="K934" t="n">
-        <v>0.115</v>
+        <v>0.124</v>
       </c>
       <c r="L934" t="n">
-        <v>0.88</v>
+        <v>0.951</v>
       </c>
       <c r="M934" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.722</v>
       </c>
       <c r="N934" t="n">
-        <v>1.158</v>
+        <v>1.211</v>
       </c>
       <c r="O934" t="b">
         <v>1</v>
@@ -72330,22 +72459,22 @@
         <v>0</v>
       </c>
       <c r="I935" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J935" t="n">
-        <v>0.149</v>
+        <v>0.112</v>
       </c>
       <c r="K935" t="n">
         <v>0.11</v>
       </c>
       <c r="L935" t="n">
-        <v>0.74</v>
+        <v>0.983</v>
       </c>
       <c r="M935" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.716</v>
       </c>
       <c r="N935" t="n">
-        <v>0.904</v>
+        <v>1.353</v>
       </c>
       <c r="O935" t="b">
         <v>1</v>
@@ -72555,10 +72684,10 @@
         <v>0.63</v>
       </c>
       <c r="M939" t="n">
-        <v>-0.427</v>
+        <v>-0.334</v>
       </c>
       <c r="N939" t="n">
-        <v>1.617</v>
+        <v>1.645</v>
       </c>
       <c r="O939" t="b">
         <v>1</v>
@@ -72666,10 +72795,10 @@
         <v>1.191</v>
       </c>
       <c r="M941" t="n">
-        <v>0.647</v>
+        <v>0.66</v>
       </c>
       <c r="N941" t="n">
-        <v>1.99</v>
+        <v>2.073</v>
       </c>
       <c r="O941" t="b">
         <v>1</v>
@@ -72726,10 +72855,10 @@
         <v>1.503</v>
       </c>
       <c r="M942" t="n">
-        <v>0.956</v>
+        <v>0.966</v>
       </c>
       <c r="N942" t="n">
-        <v>2.274</v>
+        <v>2.292</v>
       </c>
       <c r="O942" t="b">
         <v>1</v>
@@ -72786,10 +72915,10 @@
         <v>1.517</v>
       </c>
       <c r="M943" t="n">
-        <v>1.049</v>
+        <v>1.024</v>
       </c>
       <c r="N943" t="n">
-        <v>2.206</v>
+        <v>2.2</v>
       </c>
       <c r="O943" t="b">
         <v>1</v>
@@ -72846,10 +72975,10 @@
         <v>1.756</v>
       </c>
       <c r="M944" t="n">
-        <v>1.315</v>
+        <v>1.301</v>
       </c>
       <c r="N944" t="n">
-        <v>2.425</v>
+        <v>2.398</v>
       </c>
       <c r="O944" t="b">
         <v>1</v>
@@ -72906,10 +73035,10 @@
         <v>1.282</v>
       </c>
       <c r="M945" t="n">
-        <v>1.009</v>
+        <v>1.028</v>
       </c>
       <c r="N945" t="n">
-        <v>1.586</v>
+        <v>1.583</v>
       </c>
       <c r="O945" t="b">
         <v>1</v>
@@ -72969,7 +73098,7 @@
         <v>1.166</v>
       </c>
       <c r="N946" t="n">
-        <v>1.815</v>
+        <v>1.813</v>
       </c>
       <c r="O946" t="b">
         <v>1</v>
@@ -77178,16 +77307,16 @@
         <v>1</v>
       </c>
       <c r="I1017" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J1017" t="n">
-        <v>-0.029</v>
+        <v>0.005</v>
       </c>
       <c r="K1017" t="n">
-        <v>-0.007</v>
+        <v>-0.008</v>
       </c>
       <c r="O1017" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1017" t="n">
         <v>0.05</v>
@@ -77229,13 +77358,13 @@
         <v>1</v>
       </c>
       <c r="I1018" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J1018" t="n">
-        <v>0.002</v>
+        <v>0.03</v>
       </c>
       <c r="K1018" t="n">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
       <c r="O1018" t="b">
         <v>1</v>
@@ -77280,13 +77409,22 @@
         <v>1</v>
       </c>
       <c r="I1019" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="J1019" t="n">
-        <v>0.045</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="K1019" t="n">
-        <v>0.052</v>
+        <v>0.059</v>
+      </c>
+      <c r="L1019" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M1019" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="N1019" t="n">
+        <v>1.213</v>
       </c>
       <c r="O1019" t="b">
         <v>1</v>
@@ -77331,13 +77469,22 @@
         <v>1</v>
       </c>
       <c r="I1020" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J1020" t="n">
-        <v>0.049</v>
+        <v>0.074</v>
       </c>
       <c r="K1020" t="n">
-        <v>0.056</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L1020" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="M1020" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="N1020" t="n">
+        <v>1.475</v>
       </c>
       <c r="O1020" t="b">
         <v>1</v>
@@ -77382,22 +77529,22 @@
         <v>1</v>
       </c>
       <c r="I1021" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J1021" t="n">
-        <v>0.066</v>
+        <v>0.091</v>
       </c>
       <c r="K1021" t="n">
-        <v>0.063</v>
+        <v>0.08</v>
       </c>
       <c r="L1021" t="n">
-        <v>0.96</v>
+        <v>0.876</v>
       </c>
       <c r="M1021" t="n">
-        <v>0.635</v>
+        <v>0.489</v>
       </c>
       <c r="N1021" t="n">
-        <v>1.306</v>
+        <v>1.287</v>
       </c>
       <c r="O1021" t="b">
         <v>1</v>
@@ -77442,22 +77589,22 @@
         <v>1</v>
       </c>
       <c r="I1022" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J1022" t="n">
-        <v>0.08</v>
+        <v>0.098</v>
       </c>
       <c r="K1022" t="n">
-        <v>0.093</v>
+        <v>0.105</v>
       </c>
       <c r="L1022" t="n">
-        <v>1.153</v>
+        <v>1.076</v>
       </c>
       <c r="M1022" t="n">
-        <v>0.887</v>
+        <v>0.741</v>
       </c>
       <c r="N1022" t="n">
-        <v>1.512</v>
+        <v>1.542</v>
       </c>
       <c r="O1022" t="b">
         <v>1</v>
@@ -77502,22 +77649,22 @@
         <v>1</v>
       </c>
       <c r="I1023" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J1023" t="n">
-        <v>0.056</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K1023" t="n">
-        <v>0.062</v>
+        <v>0.073</v>
       </c>
       <c r="L1023" t="n">
-        <v>1.104</v>
+        <v>1.064</v>
       </c>
       <c r="M1023" t="n">
-        <v>0.744</v>
+        <v>0.59</v>
       </c>
       <c r="N1023" t="n">
-        <v>1.446</v>
+        <v>1.563</v>
       </c>
       <c r="O1023" t="b">
         <v>1</v>
@@ -77562,22 +77709,22 @@
         <v>1</v>
       </c>
       <c r="I1024" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J1024" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.105</v>
       </c>
       <c r="K1024" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="L1024" t="n">
-        <v>1.017</v>
+        <v>0.795</v>
       </c>
       <c r="M1024" t="n">
-        <v>0.746</v>
+        <v>0.486</v>
       </c>
       <c r="N1024" t="n">
-        <v>1.36</v>
+        <v>1.155</v>
       </c>
       <c r="O1024" t="b">
         <v>1</v>
@@ -77622,22 +77769,22 @@
         <v>1</v>
       </c>
       <c r="I1025" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J1025" t="n">
-        <v>0.123</v>
+        <v>0.131</v>
       </c>
       <c r="K1025" t="n">
-        <v>0.118</v>
+        <v>0.122</v>
       </c>
       <c r="L1025" t="n">
-        <v>0.96</v>
+        <v>0.931</v>
       </c>
       <c r="M1025" t="n">
-        <v>0.757</v>
+        <v>0.652</v>
       </c>
       <c r="N1025" t="n">
-        <v>1.265</v>
+        <v>1.232</v>
       </c>
       <c r="O1025" t="b">
         <v>1</v>
@@ -77682,22 +77829,22 @@
         <v>1</v>
       </c>
       <c r="I1026" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J1026" t="n">
-        <v>0.141</v>
+        <v>0.117</v>
       </c>
       <c r="K1026" t="n">
-        <v>0.113</v>
+        <v>0.111</v>
       </c>
       <c r="L1026" t="n">
-        <v>0.802</v>
+        <v>0.945</v>
       </c>
       <c r="M1026" t="n">
-        <v>0.642</v>
+        <v>0.638</v>
       </c>
       <c r="N1026" t="n">
-        <v>0.978</v>
+        <v>1.286</v>
       </c>
       <c r="O1026" t="b">
         <v>1</v>
@@ -77958,10 +78105,10 @@
         <v>1.832</v>
       </c>
       <c r="M1031" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="N1031" t="n">
-        <v>2.956</v>
+        <v>2.905</v>
       </c>
       <c r="O1031" t="b">
         <v>1</v>
@@ -78018,10 +78165,10 @@
         <v>2.072</v>
       </c>
       <c r="M1032" t="n">
-        <v>1.278</v>
+        <v>1.301</v>
       </c>
       <c r="N1032" t="n">
-        <v>3.522</v>
+        <v>3.452</v>
       </c>
       <c r="O1032" t="b">
         <v>1</v>
@@ -78078,10 +78225,10 @@
         <v>1.988</v>
       </c>
       <c r="M1033" t="n">
-        <v>1.379</v>
+        <v>1.373</v>
       </c>
       <c r="N1033" t="n">
-        <v>3.272</v>
+        <v>3.26</v>
       </c>
       <c r="O1033" t="b">
         <v>1</v>
@@ -78138,10 +78285,10 @@
         <v>2.263</v>
       </c>
       <c r="M1034" t="n">
-        <v>1.581</v>
+        <v>1.582</v>
       </c>
       <c r="N1034" t="n">
-        <v>3.706</v>
+        <v>3.802</v>
       </c>
       <c r="O1034" t="b">
         <v>1</v>
@@ -78198,10 +78345,10 @@
         <v>1.483</v>
       </c>
       <c r="M1035" t="n">
-        <v>1.197</v>
+        <v>1.191</v>
       </c>
       <c r="N1035" t="n">
-        <v>1.881</v>
+        <v>1.862</v>
       </c>
       <c r="O1035" t="b">
         <v>1</v>
@@ -78258,10 +78405,10 @@
         <v>1.657</v>
       </c>
       <c r="M1036" t="n">
-        <v>1.303</v>
+        <v>1.305</v>
       </c>
       <c r="N1036" t="n">
-        <v>2.151</v>
+        <v>2.168</v>
       </c>
       <c r="O1036" t="b">
         <v>1</v>
@@ -82818,13 +82965,13 @@
         <v>0</v>
       </c>
       <c r="I1114" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J1114" t="n">
-        <v>-0.007</v>
+        <v>0.003</v>
       </c>
       <c r="K1114" t="n">
-        <v>0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="O1114" t="b">
         <v>0</v>
@@ -82869,16 +83016,16 @@
         <v>0</v>
       </c>
       <c r="I1115" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J1115" t="n">
-        <v>-0.002</v>
+        <v>0.019</v>
       </c>
       <c r="K1115" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="O1115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1115" t="n">
         <v>0.05</v>
@@ -82920,13 +83067,13 @@
         <v>0</v>
       </c>
       <c r="I1116" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J1116" t="n">
-        <v>0.006</v>
+        <v>0.013</v>
       </c>
       <c r="K1116" t="n">
-        <v>0.038</v>
+        <v>0.01</v>
       </c>
       <c r="O1116" t="b">
         <v>1</v>
@@ -82971,13 +83118,22 @@
         <v>0</v>
       </c>
       <c r="I1117" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="J1117" t="n">
-        <v>0.043</v>
+        <v>0.078</v>
       </c>
       <c r="K1117" t="n">
-        <v>0.062</v>
+        <v>0.064</v>
+      </c>
+      <c r="L1117" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="M1117" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="N1117" t="n">
+        <v>1.252</v>
       </c>
       <c r="O1117" t="b">
         <v>1</v>
@@ -83022,22 +83178,22 @@
         <v>0</v>
       </c>
       <c r="I1118" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="J1118" t="n">
-        <v>0.067</v>
+        <v>0.093</v>
       </c>
       <c r="K1118" t="n">
-        <v>0.103</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L1118" t="n">
-        <v>1.529</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="M1118" t="n">
-        <v>1.12</v>
+        <v>0.539</v>
       </c>
       <c r="N1118" t="n">
-        <v>1.967</v>
+        <v>1.342</v>
       </c>
       <c r="O1118" t="b">
         <v>1</v>
@@ -83082,22 +83238,22 @@
         <v>0</v>
       </c>
       <c r="I1119" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J1119" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.112</v>
       </c>
       <c r="K1119" t="n">
-        <v>0.11</v>
+        <v>0.096</v>
       </c>
       <c r="L1119" t="n">
-        <v>1.277</v>
+        <v>0.861</v>
       </c>
       <c r="M1119" t="n">
-        <v>0.975</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="N1119" t="n">
-        <v>1.696</v>
+        <v>1.166</v>
       </c>
       <c r="O1119" t="b">
         <v>1</v>
@@ -83142,22 +83298,22 @@
         <v>0</v>
       </c>
       <c r="I1120" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J1120" t="n">
-        <v>0.074</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K1120" t="n">
-        <v>0.095</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="L1120" t="n">
-        <v>1.287</v>
+        <v>1.211</v>
       </c>
       <c r="M1120" t="n">
-        <v>0.956</v>
+        <v>0.76</v>
       </c>
       <c r="N1120" t="n">
-        <v>1.707</v>
+        <v>1.661</v>
       </c>
       <c r="O1120" t="b">
         <v>1</v>
@@ -83202,22 +83358,22 @@
         <v>0</v>
       </c>
       <c r="I1121" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J1121" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="K1121" t="n">
-        <v>0.093</v>
+        <v>0.089</v>
       </c>
       <c r="L1121" t="n">
-        <v>1.218</v>
+        <v>1.178</v>
       </c>
       <c r="M1121" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="N1121" t="n">
-        <v>1.607</v>
+        <v>1.645</v>
       </c>
       <c r="O1121" t="b">
         <v>1</v>
@@ -83262,22 +83418,22 @@
         <v>0</v>
       </c>
       <c r="I1122" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J1122" t="n">
-        <v>0.099</v>
+        <v>0.117</v>
       </c>
       <c r="K1122" t="n">
-        <v>0.11</v>
+        <v>0.112</v>
       </c>
       <c r="L1122" t="n">
-        <v>1.119</v>
+        <v>0.957</v>
       </c>
       <c r="M1122" t="n">
-        <v>0.892</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="N1122" t="n">
-        <v>1.442</v>
+        <v>1.351</v>
       </c>
       <c r="O1122" t="b">
         <v>1</v>
@@ -83322,22 +83478,22 @@
         <v>0</v>
       </c>
       <c r="I1123" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J1123" t="n">
-        <v>0.105</v>
+        <v>0.135</v>
       </c>
       <c r="K1123" t="n">
-        <v>0.14</v>
+        <v>0.137</v>
       </c>
       <c r="L1123" t="n">
-        <v>1.332</v>
+        <v>1.018</v>
       </c>
       <c r="M1123" t="n">
-        <v>1.06</v>
+        <v>0.761</v>
       </c>
       <c r="N1123" t="n">
-        <v>1.796</v>
+        <v>1.324</v>
       </c>
       <c r="O1123" t="b">
         <v>1</v>
@@ -83382,22 +83538,22 @@
         <v>0</v>
       </c>
       <c r="I1124" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J1124" t="n">
-        <v>0.149</v>
+        <v>0.178</v>
       </c>
       <c r="K1124" t="n">
-        <v>0.165</v>
+        <v>0.177</v>
       </c>
       <c r="L1124" t="n">
-        <v>1.105</v>
+        <v>0.997</v>
       </c>
       <c r="M1124" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.791</v>
       </c>
       <c r="N1124" t="n">
-        <v>1.332</v>
+        <v>1.233</v>
       </c>
       <c r="O1124" t="b">
         <v>1</v>
@@ -83658,10 +83814,10 @@
         <v>1.793</v>
       </c>
       <c r="M1129" t="n">
-        <v>1.109</v>
+        <v>1.152</v>
       </c>
       <c r="N1129" t="n">
-        <v>2.92</v>
+        <v>2.955</v>
       </c>
       <c r="O1129" t="b">
         <v>1</v>
@@ -83718,10 +83874,10 @@
         <v>2.298</v>
       </c>
       <c r="M1130" t="n">
-        <v>1.487</v>
+        <v>1.5</v>
       </c>
       <c r="N1130" t="n">
-        <v>3.783</v>
+        <v>3.861</v>
       </c>
       <c r="O1130" t="b">
         <v>1</v>
@@ -83778,10 +83934,10 @@
         <v>2.508</v>
       </c>
       <c r="M1131" t="n">
-        <v>1.667</v>
+        <v>1.684</v>
       </c>
       <c r="N1131" t="n">
-        <v>4.097</v>
+        <v>4.157</v>
       </c>
       <c r="O1131" t="b">
         <v>1</v>
@@ -83889,10 +84045,10 @@
         <v>3.063</v>
       </c>
       <c r="M1133" t="n">
-        <v>1.99</v>
+        <v>1.841</v>
       </c>
       <c r="N1133" t="n">
-        <v>4.494</v>
+        <v>4.438</v>
       </c>
       <c r="O1133" t="b">
         <v>1</v>
@@ -83949,10 +84105,10 @@
         <v>4.397</v>
       </c>
       <c r="M1134" t="n">
-        <v>2.307</v>
+        <v>2.291</v>
       </c>
       <c r="N1134" t="n">
-        <v>5.369</v>
+        <v>5.29</v>
       </c>
       <c r="O1134" t="b">
         <v>1</v>
@@ -84009,10 +84165,10 @@
         <v>4.288</v>
       </c>
       <c r="M1135" t="n">
-        <v>2.065</v>
+        <v>2.11</v>
       </c>
       <c r="N1135" t="n">
-        <v>5.096</v>
+        <v>5.019</v>
       </c>
       <c r="O1135" t="b">
         <v>1</v>
@@ -88212,13 +88368,13 @@
         <v>1</v>
       </c>
       <c r="I1206" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="J1206" t="n">
-        <v>0.005</v>
+        <v>0.022</v>
       </c>
       <c r="K1206" t="n">
-        <v>0.02</v>
+        <v>0.031</v>
       </c>
       <c r="O1206" t="b">
         <v>1</v>
@@ -88263,13 +88419,13 @@
         <v>1</v>
       </c>
       <c r="I1207" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J1207" t="n">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="K1207" t="n">
-        <v>0.035</v>
+        <v>0.008</v>
       </c>
       <c r="O1207" t="b">
         <v>1</v>
@@ -88314,13 +88470,22 @@
         <v>1</v>
       </c>
       <c r="I1208" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="J1208" t="n">
-        <v>0.05</v>
+        <v>0.074</v>
       </c>
       <c r="K1208" t="n">
-        <v>0.059</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L1208" t="n">
+        <v>0.954</v>
+      </c>
+      <c r="M1208" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="N1208" t="n">
+        <v>1.328</v>
       </c>
       <c r="O1208" t="b">
         <v>1</v>
@@ -88365,22 +88530,22 @@
         <v>1</v>
       </c>
       <c r="I1209" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="J1209" t="n">
-        <v>0.075</v>
+        <v>0.092</v>
       </c>
       <c r="K1209" t="n">
-        <v>0.1</v>
+        <v>0.094</v>
       </c>
       <c r="L1209" t="n">
-        <v>1.334</v>
+        <v>1.029</v>
       </c>
       <c r="M1209" t="n">
-        <v>0.921</v>
+        <v>0.703</v>
       </c>
       <c r="N1209" t="n">
-        <v>1.833</v>
+        <v>1.423</v>
       </c>
       <c r="O1209" t="b">
         <v>1</v>
@@ -88425,22 +88590,22 @@
         <v>1</v>
       </c>
       <c r="I1210" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J1210" t="n">
-        <v>0.093</v>
+        <v>0.107</v>
       </c>
       <c r="K1210" t="n">
-        <v>0.107</v>
+        <v>0.097</v>
       </c>
       <c r="L1210" t="n">
-        <v>1.141</v>
+        <v>0.901</v>
       </c>
       <c r="M1210" t="n">
-        <v>0.863</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="N1210" t="n">
-        <v>1.531</v>
+        <v>1.207</v>
       </c>
       <c r="O1210" t="b">
         <v>1</v>
@@ -88485,22 +88650,22 @@
         <v>1</v>
       </c>
       <c r="I1211" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J1211" t="n">
-        <v>0.081</v>
+        <v>0.075</v>
       </c>
       <c r="K1211" t="n">
-        <v>0.092</v>
+        <v>0.093</v>
       </c>
       <c r="L1211" t="n">
-        <v>1.13</v>
+        <v>1.249</v>
       </c>
       <c r="M1211" t="n">
-        <v>0.791</v>
+        <v>0.891</v>
       </c>
       <c r="N1211" t="n">
-        <v>1.547</v>
+        <v>1.682</v>
       </c>
       <c r="O1211" t="b">
         <v>1</v>
@@ -88545,22 +88710,22 @@
         <v>1</v>
       </c>
       <c r="I1212" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J1212" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.079</v>
       </c>
       <c r="K1212" t="n">
-        <v>0.09</v>
+        <v>0.095</v>
       </c>
       <c r="L1212" t="n">
-        <v>1.071</v>
+        <v>1.202</v>
       </c>
       <c r="M1212" t="n">
-        <v>0.721</v>
+        <v>0.856</v>
       </c>
       <c r="N1212" t="n">
-        <v>1.468</v>
+        <v>1.61</v>
       </c>
       <c r="O1212" t="b">
         <v>1</v>
@@ -88605,22 +88770,22 @@
         <v>1</v>
       </c>
       <c r="I1213" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J1213" t="n">
-        <v>0.106</v>
+        <v>0.119</v>
       </c>
       <c r="K1213" t="n">
-        <v>0.107</v>
+        <v>0.117</v>
       </c>
       <c r="L1213" t="n">
-        <v>1.01</v>
+        <v>0.986</v>
       </c>
       <c r="M1213" t="n">
-        <v>0.773</v>
+        <v>0.757</v>
       </c>
       <c r="N1213" t="n">
-        <v>1.289</v>
+        <v>1.297</v>
       </c>
       <c r="O1213" t="b">
         <v>1</v>
@@ -88665,22 +88830,22 @@
         <v>1</v>
       </c>
       <c r="I1214" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J1214" t="n">
-        <v>0.113</v>
+        <v>0.14</v>
       </c>
       <c r="K1214" t="n">
-        <v>0.137</v>
+        <v>0.144</v>
       </c>
       <c r="L1214" t="n">
-        <v>1.216</v>
+        <v>1.026</v>
       </c>
       <c r="M1214" t="n">
-        <v>0.923</v>
+        <v>0.827</v>
       </c>
       <c r="N1214" t="n">
-        <v>1.657</v>
+        <v>1.281</v>
       </c>
       <c r="O1214" t="b">
         <v>1</v>
@@ -88725,22 +88890,22 @@
         <v>1</v>
       </c>
       <c r="I1215" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J1215" t="n">
-        <v>0.156</v>
+        <v>0.176</v>
       </c>
       <c r="K1215" t="n">
-        <v>0.161</v>
+        <v>0.178</v>
       </c>
       <c r="L1215" t="n">
-        <v>1.032</v>
+        <v>1.012</v>
       </c>
       <c r="M1215" t="n">
-        <v>0.851</v>
+        <v>0.848</v>
       </c>
       <c r="N1215" t="n">
-        <v>1.22</v>
+        <v>1.209</v>
       </c>
       <c r="O1215" t="b">
         <v>1</v>
@@ -88851,7 +89016,7 @@
         <v>-0.367</v>
       </c>
       <c r="N1217" t="n">
-        <v>1.81</v>
+        <v>1.802</v>
       </c>
       <c r="O1217" t="b">
         <v>1</v>
@@ -88908,10 +89073,10 @@
         <v>1.8</v>
       </c>
       <c r="M1218" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="N1218" t="n">
-        <v>3.157</v>
+        <v>3.037</v>
       </c>
       <c r="O1218" t="b">
         <v>1</v>
@@ -88968,10 +89133,10 @@
         <v>1.32</v>
       </c>
       <c r="M1219" t="n">
-        <v>0.804</v>
+        <v>0.823</v>
       </c>
       <c r="N1219" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O1219" t="b">
         <v>1</v>
@@ -89028,10 +89193,10 @@
         <v>1.701</v>
       </c>
       <c r="M1220" t="n">
-        <v>1.213</v>
+        <v>1.168</v>
       </c>
       <c r="N1220" t="n">
-        <v>2.434</v>
+        <v>2.405</v>
       </c>
       <c r="O1220" t="b">
         <v>1</v>
@@ -89088,10 +89253,10 @@
         <v>1.839</v>
       </c>
       <c r="M1221" t="n">
-        <v>1.261</v>
+        <v>1.224</v>
       </c>
       <c r="N1221" t="n">
-        <v>2.793</v>
+        <v>2.735</v>
       </c>
       <c r="O1221" t="b">
         <v>1</v>
@@ -89148,10 +89313,10 @@
         <v>2.466</v>
       </c>
       <c r="M1222" t="n">
-        <v>1.652</v>
+        <v>1.63</v>
       </c>
       <c r="N1222" t="n">
-        <v>3.706</v>
+        <v>3.731</v>
       </c>
       <c r="O1222" t="b">
         <v>1</v>
@@ -89208,10 +89373,10 @@
         <v>2.039</v>
       </c>
       <c r="M1223" t="n">
-        <v>1.368</v>
+        <v>1.35</v>
       </c>
       <c r="N1223" t="n">
-        <v>3.257</v>
+        <v>3.333</v>
       </c>
       <c r="O1223" t="b">
         <v>1</v>
@@ -89268,10 +89433,10 @@
         <v>2.622</v>
       </c>
       <c r="M1224" t="n">
-        <v>1.645</v>
+        <v>1.646</v>
       </c>
       <c r="N1224" t="n">
-        <v>4.17</v>
+        <v>4.227</v>
       </c>
       <c r="O1224" t="b">
         <v>1</v>
@@ -89328,10 +89493,10 @@
         <v>2.442</v>
       </c>
       <c r="M1225" t="n">
-        <v>1.496</v>
+        <v>1.445</v>
       </c>
       <c r="N1225" t="n">
-        <v>3.843</v>
+        <v>3.932</v>
       </c>
       <c r="O1225" t="b">
         <v>1</v>
@@ -93531,13 +93696,13 @@
         <v>1</v>
       </c>
       <c r="I1296" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="J1296" t="n">
-        <v>0.005</v>
+        <v>0.022</v>
       </c>
       <c r="K1296" t="n">
-        <v>0.02</v>
+        <v>0.031</v>
       </c>
       <c r="O1296" t="b">
         <v>1</v>
@@ -93582,13 +93747,13 @@
         <v>1</v>
       </c>
       <c r="I1297" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J1297" t="n">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="K1297" t="n">
-        <v>0.035</v>
+        <v>0.008</v>
       </c>
       <c r="O1297" t="b">
         <v>1</v>
@@ -93633,13 +93798,22 @@
         <v>1</v>
       </c>
       <c r="I1298" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="J1298" t="n">
-        <v>0.05</v>
+        <v>0.074</v>
       </c>
       <c r="K1298" t="n">
-        <v>0.059</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L1298" t="n">
+        <v>0.954</v>
+      </c>
+      <c r="M1298" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="N1298" t="n">
+        <v>1.328</v>
       </c>
       <c r="O1298" t="b">
         <v>1</v>
@@ -93684,22 +93858,22 @@
         <v>1</v>
       </c>
       <c r="I1299" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="J1299" t="n">
-        <v>0.075</v>
+        <v>0.092</v>
       </c>
       <c r="K1299" t="n">
-        <v>0.1</v>
+        <v>0.094</v>
       </c>
       <c r="L1299" t="n">
-        <v>1.334</v>
+        <v>1.029</v>
       </c>
       <c r="M1299" t="n">
-        <v>0.921</v>
+        <v>0.703</v>
       </c>
       <c r="N1299" t="n">
-        <v>1.833</v>
+        <v>1.423</v>
       </c>
       <c r="O1299" t="b">
         <v>1</v>
@@ -93744,22 +93918,22 @@
         <v>1</v>
       </c>
       <c r="I1300" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J1300" t="n">
-        <v>0.093</v>
+        <v>0.107</v>
       </c>
       <c r="K1300" t="n">
-        <v>0.107</v>
+        <v>0.097</v>
       </c>
       <c r="L1300" t="n">
-        <v>1.141</v>
+        <v>0.901</v>
       </c>
       <c r="M1300" t="n">
-        <v>0.863</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="N1300" t="n">
-        <v>1.531</v>
+        <v>1.207</v>
       </c>
       <c r="O1300" t="b">
         <v>1</v>
@@ -93804,22 +93978,22 @@
         <v>1</v>
       </c>
       <c r="I1301" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J1301" t="n">
-        <v>0.081</v>
+        <v>0.075</v>
       </c>
       <c r="K1301" t="n">
-        <v>0.092</v>
+        <v>0.093</v>
       </c>
       <c r="L1301" t="n">
-        <v>1.13</v>
+        <v>1.249</v>
       </c>
       <c r="M1301" t="n">
-        <v>0.791</v>
+        <v>0.891</v>
       </c>
       <c r="N1301" t="n">
-        <v>1.547</v>
+        <v>1.682</v>
       </c>
       <c r="O1301" t="b">
         <v>1</v>
@@ -93864,22 +94038,22 @@
         <v>1</v>
       </c>
       <c r="I1302" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J1302" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.079</v>
       </c>
       <c r="K1302" t="n">
-        <v>0.09</v>
+        <v>0.095</v>
       </c>
       <c r="L1302" t="n">
-        <v>1.071</v>
+        <v>1.202</v>
       </c>
       <c r="M1302" t="n">
-        <v>0.721</v>
+        <v>0.856</v>
       </c>
       <c r="N1302" t="n">
-        <v>1.468</v>
+        <v>1.61</v>
       </c>
       <c r="O1302" t="b">
         <v>1</v>
@@ -93924,22 +94098,22 @@
         <v>1</v>
       </c>
       <c r="I1303" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J1303" t="n">
-        <v>0.106</v>
+        <v>0.119</v>
       </c>
       <c r="K1303" t="n">
-        <v>0.107</v>
+        <v>0.117</v>
       </c>
       <c r="L1303" t="n">
-        <v>1.01</v>
+        <v>0.986</v>
       </c>
       <c r="M1303" t="n">
-        <v>0.773</v>
+        <v>0.757</v>
       </c>
       <c r="N1303" t="n">
-        <v>1.289</v>
+        <v>1.297</v>
       </c>
       <c r="O1303" t="b">
         <v>1</v>
@@ -93984,22 +94158,22 @@
         <v>1</v>
       </c>
       <c r="I1304" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J1304" t="n">
-        <v>0.113</v>
+        <v>0.14</v>
       </c>
       <c r="K1304" t="n">
-        <v>0.137</v>
+        <v>0.144</v>
       </c>
       <c r="L1304" t="n">
-        <v>1.216</v>
+        <v>1.026</v>
       </c>
       <c r="M1304" t="n">
-        <v>0.923</v>
+        <v>0.827</v>
       </c>
       <c r="N1304" t="n">
-        <v>1.657</v>
+        <v>1.281</v>
       </c>
       <c r="O1304" t="b">
         <v>1</v>
@@ -94044,22 +94218,22 @@
         <v>1</v>
       </c>
       <c r="I1305" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J1305" t="n">
-        <v>0.156</v>
+        <v>0.176</v>
       </c>
       <c r="K1305" t="n">
-        <v>0.161</v>
+        <v>0.178</v>
       </c>
       <c r="L1305" t="n">
-        <v>1.032</v>
+        <v>1.012</v>
       </c>
       <c r="M1305" t="n">
-        <v>0.851</v>
+        <v>0.848</v>
       </c>
       <c r="N1305" t="n">
-        <v>1.22</v>
+        <v>1.209</v>
       </c>
       <c r="O1305" t="b">
         <v>1</v>
@@ -94170,7 +94344,7 @@
         <v>-0.367</v>
       </c>
       <c r="N1307" t="n">
-        <v>1.81</v>
+        <v>1.802</v>
       </c>
       <c r="O1307" t="b">
         <v>1</v>
@@ -94227,10 +94401,10 @@
         <v>1.8</v>
       </c>
       <c r="M1308" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="N1308" t="n">
-        <v>3.157</v>
+        <v>3.037</v>
       </c>
       <c r="O1308" t="b">
         <v>1</v>
@@ -94287,10 +94461,10 @@
         <v>1.32</v>
       </c>
       <c r="M1309" t="n">
-        <v>0.804</v>
+        <v>0.823</v>
       </c>
       <c r="N1309" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O1309" t="b">
         <v>1</v>
@@ -94347,10 +94521,10 @@
         <v>1.701</v>
       </c>
       <c r="M1310" t="n">
-        <v>1.213</v>
+        <v>1.168</v>
       </c>
       <c r="N1310" t="n">
-        <v>2.434</v>
+        <v>2.405</v>
       </c>
       <c r="O1310" t="b">
         <v>1</v>
@@ -94407,10 +94581,10 @@
         <v>1.839</v>
       </c>
       <c r="M1311" t="n">
-        <v>1.261</v>
+        <v>1.224</v>
       </c>
       <c r="N1311" t="n">
-        <v>2.793</v>
+        <v>2.735</v>
       </c>
       <c r="O1311" t="b">
         <v>1</v>
@@ -94467,10 +94641,10 @@
         <v>2.466</v>
       </c>
       <c r="M1312" t="n">
-        <v>1.652</v>
+        <v>1.63</v>
       </c>
       <c r="N1312" t="n">
-        <v>3.706</v>
+        <v>3.731</v>
       </c>
       <c r="O1312" t="b">
         <v>1</v>
@@ -94527,10 +94701,10 @@
         <v>2.039</v>
       </c>
       <c r="M1313" t="n">
-        <v>1.368</v>
+        <v>1.35</v>
       </c>
       <c r="N1313" t="n">
-        <v>3.257</v>
+        <v>3.333</v>
       </c>
       <c r="O1313" t="b">
         <v>1</v>
@@ -94587,10 +94761,10 @@
         <v>2.622</v>
       </c>
       <c r="M1314" t="n">
-        <v>1.645</v>
+        <v>1.646</v>
       </c>
       <c r="N1314" t="n">
-        <v>4.17</v>
+        <v>4.227</v>
       </c>
       <c r="O1314" t="b">
         <v>1</v>
@@ -94647,10 +94821,10 @@
         <v>2.442</v>
       </c>
       <c r="M1315" t="n">
-        <v>1.496</v>
+        <v>1.445</v>
       </c>
       <c r="N1315" t="n">
-        <v>3.843</v>
+        <v>3.932</v>
       </c>
       <c r="O1315" t="b">
         <v>1</v>
@@ -94961,10 +95135,10 @@
         <v>1.832</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>2.956</v>
+        <v>2.905</v>
       </c>
       <c r="I6" t="n">
         <v>0.148</v>
@@ -94976,10 +95150,10 @@
         <v>1.701</v>
       </c>
       <c r="L6" t="n">
-        <v>1.213</v>
+        <v>1.168</v>
       </c>
       <c r="M6" t="n">
-        <v>2.434</v>
+        <v>2.405</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -95201,10 +95375,10 @@
         <v>1.657</v>
       </c>
       <c r="G11" t="n">
-        <v>1.303</v>
+        <v>1.305</v>
       </c>
       <c r="H11" t="n">
-        <v>2.151</v>
+        <v>2.168</v>
       </c>
       <c r="I11" t="n">
         <v>0.08599999999999999</v>
@@ -95216,10 +95390,10 @@
         <v>2.442</v>
       </c>
       <c r="L11" t="n">
-        <v>1.496</v>
+        <v>1.445</v>
       </c>
       <c r="M11" t="n">
-        <v>3.843</v>
+        <v>3.932</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
@@ -95441,10 +95615,10 @@
         <v>3.713</v>
       </c>
       <c r="G16" t="n">
-        <v>2.183</v>
+        <v>2.113</v>
       </c>
       <c r="H16" t="n">
-        <v>5.057</v>
+        <v>5.127</v>
       </c>
       <c r="I16" t="n">
         <v>0.131</v>
@@ -95456,10 +95630,10 @@
         <v>2.44</v>
       </c>
       <c r="L16" t="n">
-        <v>1.748</v>
+        <v>1.738</v>
       </c>
       <c r="M16" t="n">
-        <v>3.813</v>
+        <v>3.946</v>
       </c>
       <c r="N16" t="b">
         <v>0</v>
@@ -95684,7 +95858,7 @@
         <v>0.944</v>
       </c>
       <c r="H21" t="n">
-        <v>1.21</v>
+        <v>1.208</v>
       </c>
       <c r="I21" t="n">
         <v>0.001</v>
